--- a/cert_tracker/Contractor Certifications Tracker.xlsx
+++ b/cert_tracker/Contractor Certifications Tracker.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsant\jacobdashboard\cert_tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005802A7-5560-4D73-8058-7581EBAAC684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851FFCEC-3A94-489A-A63E-B0D2EFC83723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
-    <sheet name="Certifications" sheetId="3" r:id="rId3"/>
-    <sheet name="Contractors" sheetId="4" r:id="rId4"/>
-    <sheet name="Workers" sheetId="5" r:id="rId5"/>
-    <sheet name="Tracker" sheetId="6" r:id="rId6"/>
+    <sheet name="Certifications" sheetId="2" r:id="rId2"/>
+    <sheet name="Contractors" sheetId="3" r:id="rId3"/>
+    <sheet name="Workers" sheetId="4" r:id="rId4"/>
+    <sheet name="Tracker" sheetId="5" r:id="rId5"/>
+    <sheet name="Dashboard" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Tracker!$A$2:$AC$200</definedName>
     <definedName name="ContractorOption" comment="=Workers!$B$2:INDEX(Workers!$B:$B,LOOKUP(2,1/(Workers!$B:$B&lt;&gt;&quot;&quot;),ROW(Workers!$B:$B)))">Workers!$B$2:INDEX(Workers!$B:$B,LOOKUP(2,1/(Workers!$B:$B&lt;&gt;""),ROW(Workers!$B:$B)))</definedName>
     <definedName name="JobTitleOptions">Workers!$C$2:INDEX(Workers!$C:$C,LOOKUP(2,1/(Workers!$C:$C&lt;&gt;""),ROW(Workers!$C:$C)))</definedName>
   </definedNames>
@@ -42,90 +43,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="98">
   <si>
-    <t>Worker Name</t>
+    <t>Contractor Certifications Dashboard</t>
   </si>
   <si>
-    <t>Contractor</t>
+    <t>Total Contractors</t>
   </si>
   <si>
-    <t>Job Title</t>
+    <t>Total Workers</t>
   </si>
   <si>
-    <t>Status</t>
+    <t>Active Workers</t>
   </si>
   <si>
-    <t>Employee Code</t>
+    <t>Today</t>
   </si>
   <si>
-    <t>Hire Date</t>
+    <t>Compliance by Certification</t>
   </si>
   <si>
-    <t>Email</t>
+    <t>Certification</t>
   </si>
   <si>
-    <t>Phone</t>
+    <t>Category</t>
   </si>
   <si>
-    <t>Notes</t>
+    <t>Completed</t>
   </si>
   <si>
-    <t>William Rodriguez Rivera</t>
+    <t>Missing</t>
   </si>
   <si>
-    <t>GeoEnviroTech, Inc.</t>
+    <t>% Complete</t>
   </si>
   <si>
-    <t>Project Geologist</t>
-  </si>
-  <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>Hardy Rodríguez Vázquez</t>
-  </si>
-  <si>
-    <t>Civil Constructor</t>
-  </si>
-  <si>
-    <t>Juan D. Negrón Hernández</t>
-  </si>
-  <si>
-    <t>Rafael Díaz Colón</t>
-  </si>
-  <si>
-    <t>Luis A. Padilla Díaz</t>
-  </si>
-  <si>
-    <t>Jesús Quiñonez Ayala</t>
-  </si>
-  <si>
-    <t>Héctor M. Rodríguez Alicea</t>
-  </si>
-  <si>
-    <t>Cornerstone Industrial Group, Corp</t>
-  </si>
-  <si>
-    <t>Rene J. Torres Blasini</t>
-  </si>
-  <si>
-    <t>Jorge L. Figueroa Torres</t>
-  </si>
-  <si>
-    <t>Giovani Torres</t>
-  </si>
-  <si>
-    <t>Santos Rivera Tirado</t>
-  </si>
-  <si>
-    <t>José J. Rincon</t>
-  </si>
-  <si>
-    <t>Carlos O. Luhring</t>
-  </si>
-  <si>
-    <t>Felipe Lopez Dinardi</t>
+    <t>Bar</t>
   </si>
   <si>
     <t>Contractor Certifications Tracker</t>
@@ -173,46 +126,16 @@
     <t>Every edit is tracked in Version History (File → Info → Version History).</t>
   </si>
   <si>
+    <t>Notes</t>
+  </si>
+  <si>
     <t>• Validity years in the Certifications tab drive expiration logic. 0 = no expiration.</t>
   </si>
   <si>
     <t>• Dates must be entered as real dates (mm/dd/yyyy), not text.</t>
   </si>
   <si>
-    <t>Contractor Certifications Dashboard</t>
-  </si>
-  <si>
-    <t>Total Contractors</t>
-  </si>
-  <si>
-    <t>Total Workers</t>
-  </si>
-  <si>
-    <t>Active Workers</t>
-  </si>
-  <si>
-    <t>Today</t>
-  </si>
-  <si>
-    <t>Compliance by Certification</t>
-  </si>
-  <si>
-    <t>Certification</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>Missing</t>
-  </si>
-  <si>
-    <t>% Complete</t>
-  </si>
-  <si>
-    <t>Bar</t>
+    <t>Validity (years, 0=none)</t>
   </si>
   <si>
     <t>Protección Contra Caídas</t>
@@ -275,9 +198,6 @@
     <t>Utility Locating</t>
   </si>
   <si>
-    <t>Validity (years, 0=none)</t>
-  </si>
-  <si>
     <t>OSHA 10</t>
   </si>
   <si>
@@ -296,6 +216,15 @@
     <t>Concrete &amp; Masonry</t>
   </si>
   <si>
+    <t>Equipment Training</t>
+  </si>
+  <si>
+    <t>OSHA 30 501</t>
+  </si>
+  <si>
+    <t>OSHA 30 511</t>
+  </si>
+  <si>
     <t>Contractor Name</t>
   </si>
   <si>
@@ -308,13 +237,100 @@
     <t>Workers (count)</t>
   </si>
   <si>
+    <t>GeoEnviroTech, Inc.</t>
+  </si>
+  <si>
     <t>Juan D. Negrón, PG</t>
   </si>
   <si>
     <t>Drilling / Geotechnical</t>
   </si>
   <si>
+    <t>Cornerstone Industrial Group, Corp</t>
+  </si>
+  <si>
+    <t>Felipe Lopez Dinardi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Civil Construction                                                                    </t>
+  </si>
+  <si>
+    <t>Worker Name</t>
+  </si>
+  <si>
+    <t>Contractor</t>
+  </si>
+  <si>
+    <t>Job Title</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Employee Code</t>
+  </si>
+  <si>
+    <t>Hire Date</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>William Rodriguez Rivera</t>
+  </si>
+  <si>
+    <t>Project Geologist</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Hardy Rodríguez Vázquez</t>
+  </si>
+  <si>
+    <t>Juan D. Negrón Hernández</t>
+  </si>
+  <si>
+    <t>Rafael Díaz Colón</t>
+  </si>
+  <si>
+    <t>Luis A. Padilla Díaz</t>
+  </si>
+  <si>
+    <t>Jesús Quiñonez Ayala</t>
+  </si>
+  <si>
+    <t>Héctor M. Rodríguez Alicea</t>
+  </si>
+  <si>
+    <t>Civil Constructor</t>
+  </si>
+  <si>
+    <t>Rene J. Torres Blasini</t>
+  </si>
+  <si>
+    <t>Jorge L. Figueroa Torres</t>
+  </si>
+  <si>
+    <t>Giovani Torres</t>
+  </si>
+  <si>
+    <t>Santos Rivera Tirado</t>
+  </si>
+  <si>
+    <t>José J. Rincon</t>
+  </si>
+  <si>
+    <t>Carlos O. Luhring</t>
+  </si>
+  <si>
+    <t>Francisco González Carmona</t>
+  </si>
+  <si>
+    <t>Steven Cruz Martínez</t>
   </si>
   <si>
     <t>HSE Required Certifications</t>
@@ -331,7 +347,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -387,6 +403,11 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2E7D32"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -411,7 +432,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -434,11 +455,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -458,15 +494,18 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -474,18 +513,67 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8CBAD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -546,7 +634,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Contractor Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Primary Contact"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Specialty"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Workers (count)" dataDxfId="5">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Workers (count)" dataDxfId="12">
       <calculatedColumnFormula>IF(A2="","",COUNTIF(Workers!B:B,A2))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Notes"/>
@@ -570,41 +658,6 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="TrackerTable" displayName="TrackerTable" ref="A2:Z200">
-  <autoFilter ref="A2:Z200" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
-  <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Contractor"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Worker"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Protección Contra Caídas"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Flama Expuesta"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Espacios Confinados"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Manejo de Equipo Motorizado"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Excavación o Zanja"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Manejo de Tijeras (Scissor Lift)"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Seguridad Eléctrica"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Lockout"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Manejo de Grúas"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="Escaleras"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="Andamios"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="Trabajos con Plomo o Asbesto"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="Comunicación de Riesgos"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="Inducción Jacobs/Lilly"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="OSHA 40Hr HAZWOPER"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="OSHA 8Hr Refresher"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="Drilling Safety"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="Utility Locating"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="OSHA 10"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0300-000016000000}" name="OSHA 30"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0300-000017000000}" name="Rebar Safety"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0300-000018000000}" name="Formwork &amp; Shoring"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0300-000019000000}" name="Silica Exposure"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0300-00001A000000}" name="Concrete &amp; Masonry"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -900,46 +953,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="A1" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -947,27 +1000,27 @@
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -975,17 +1028,17 @@
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -993,17 +1046,17 @@
     </row>
     <row r="20" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1016,572 +1069,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" s="12"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
-        <f>COUNTA(Contractors!A2:A50)</f>
-        <v>2</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="13">
-        <f>COUNTA(Workers!A2:A200)</f>
-        <v>14</v>
-      </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="13">
-        <f>COUNTIFS(Workers!A2:A200,"&lt;&gt;",Workers!D2:D200,"active")</f>
-        <v>14</v>
-      </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13" t="str">
-        <f ca="1">TEXT(TODAY(),"mm/dd/yyyy")</f>
-        <v>04/22/2026</v>
-      </c>
-      <c r="H4" s="12"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-    </row>
-    <row r="7" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="2">
-        <f>COUNTA(Tracker!C3:C200)</f>
-        <v>14</v>
-      </c>
-      <c r="D9" s="2">
-        <f>COUNTA(Workers!A2:A200)-C9</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="3">
-        <f t="shared" ref="E9:E26" si="0">IFERROR(C9/(C9+D9),0)</f>
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="str">
-        <f t="shared" ref="F9:F26" si="1">REPT("■",ROUND(E9*20,0))</f>
-        <v>■■■■■■■■■■■■■■■■■■■■</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="2">
-        <f>COUNTA(Tracker!D3:D200)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <f>COUNTA(Workers!A2:A200)-C10</f>
-        <v>14</v>
-      </c>
-      <c r="E10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="2">
-        <f>COUNTA(Tracker!E3:E200)</f>
-        <v>8</v>
-      </c>
-      <c r="D11" s="2">
-        <f>COUNTA(Workers!A2:A200)-C11</f>
-        <v>6</v>
-      </c>
-      <c r="E11" s="3">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="F11" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■■■■■■■■■</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="2">
-        <f>COUNTA(Tracker!F3:F200)</f>
-        <v>3</v>
-      </c>
-      <c r="D12" s="2">
-        <f>COUNTA(Workers!A2:A200)-C12</f>
-        <v>11</v>
-      </c>
-      <c r="E12" s="3">
-        <f t="shared" si="0"/>
-        <v>0.21428571428571427</v>
-      </c>
-      <c r="F12" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■■</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="2">
-        <f>COUNTA(Tracker!G3:G200)</f>
-        <v>8</v>
-      </c>
-      <c r="D13" s="2">
-        <f>COUNTA(Workers!A2:A200)-C13</f>
-        <v>6</v>
-      </c>
-      <c r="E13" s="3">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="F13" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■■■■■■■■■</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="2">
-        <f>COUNTA(Tracker!H3:H200)</f>
-        <v>8</v>
-      </c>
-      <c r="D14" s="2">
-        <f>COUNTA(Workers!A2:A200)-C14</f>
-        <v>6</v>
-      </c>
-      <c r="E14" s="3">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■■■■■■■■■</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="2">
-        <f>COUNTA(Tracker!I3:I200)</f>
-        <v>9</v>
-      </c>
-      <c r="D15" s="2">
-        <f>COUNTA(Workers!A2:A200)-C15</f>
-        <v>5</v>
-      </c>
-      <c r="E15" s="3">
-        <f t="shared" si="0"/>
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="F15" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■■■■■■■■■■■</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="2">
-        <f>COUNTA(Tracker!J3:J200)</f>
-        <v>9</v>
-      </c>
-      <c r="D16" s="2">
-        <f>COUNTA(Workers!A2:A200)-C16</f>
-        <v>5</v>
-      </c>
-      <c r="E16" s="3">
-        <f t="shared" si="0"/>
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■■■■■■■■■■■</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="2">
-        <f>COUNTA(Tracker!K3:K200)</f>
-        <v>3</v>
-      </c>
-      <c r="D17" s="2">
-        <f>COUNTA(Workers!A2:A200)-C17</f>
-        <v>11</v>
-      </c>
-      <c r="E17" s="3">
-        <f t="shared" si="0"/>
-        <v>0.21428571428571427</v>
-      </c>
-      <c r="F17" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■■</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="2">
-        <f>COUNTA(Tracker!L3:L200)</f>
-        <v>8</v>
-      </c>
-      <c r="D18" s="2">
-        <f>COUNTA(Workers!A2:A200)-C18</f>
-        <v>6</v>
-      </c>
-      <c r="E18" s="3">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■■■■■■■■■</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="2">
-        <f>COUNTA(Tracker!M3:M200)</f>
-        <v>3</v>
-      </c>
-      <c r="D19" s="2">
-        <f>COUNTA(Workers!A2:A200)-C19</f>
-        <v>11</v>
-      </c>
-      <c r="E19" s="3">
-        <f t="shared" si="0"/>
-        <v>0.21428571428571427</v>
-      </c>
-      <c r="F19" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■■</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="2">
-        <f>COUNTA(Tracker!N3:N200)</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="2">
-        <f>COUNTA(Workers!A2:A200)-C20</f>
-        <v>14</v>
-      </c>
-      <c r="E20" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="2">
-        <f>COUNTA(Tracker!O3:O200)</f>
-        <v>14</v>
-      </c>
-      <c r="D21" s="2">
-        <f>COUNTA(Workers!A2:A200)-C21</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F21" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■■■■■■■■■■■■■■■■■■</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" s="2">
-        <f>COUNTA(Tracker!P3:P200)</f>
-        <v>5</v>
-      </c>
-      <c r="D22" s="2">
-        <f>COUNTA(Workers!A2:A200)-C22</f>
-        <v>9</v>
-      </c>
-      <c r="E22" s="3">
-        <f t="shared" si="0"/>
-        <v>0.35714285714285715</v>
-      </c>
-      <c r="F22" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■■■■■</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" s="2">
-        <f>COUNTA(Tracker!Q3:Q200)</f>
-        <v>6</v>
-      </c>
-      <c r="D23" s="2">
-        <f>COUNTA(Workers!A2:A200)-C23</f>
-        <v>8</v>
-      </c>
-      <c r="E23" s="3">
-        <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="F23" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■■■■■■■</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="2">
-        <f>COUNTA(Tracker!R3:R200)</f>
-        <v>6</v>
-      </c>
-      <c r="D24" s="2">
-        <f>COUNTA(Workers!A2:A200)-C24</f>
-        <v>8</v>
-      </c>
-      <c r="E24" s="3">
-        <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="F24" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■■■■■■■</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="2">
-        <f>COUNTA(Tracker!S3:S200)</f>
-        <v>6</v>
-      </c>
-      <c r="D25" s="2">
-        <f>COUNTA(Workers!A2:A200)-C25</f>
-        <v>8</v>
-      </c>
-      <c r="E25" s="3">
-        <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="F25" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■■■■■■■</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="2">
-        <f>COUNTA(Tracker!T3:T200)</f>
-        <v>2</v>
-      </c>
-      <c r="D26" s="2">
-        <f>COUNTA(Workers!A2:A200)-C26</f>
-        <v>12</v>
-      </c>
-      <c r="E26" s="3">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>■■■</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="G4:H5"/>
-    <mergeCell ref="E4:F5"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E9:E26">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
-      <formula>0.7</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="between">
-      <formula>0.7</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1592,24 +1080,24 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1617,10 +1105,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1628,10 +1116,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1639,10 +1127,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -1650,10 +1138,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1661,10 +1149,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -1672,10 +1160,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1683,10 +1171,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1694,10 +1182,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -1705,10 +1193,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -1716,10 +1204,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -1727,10 +1215,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1738,10 +1226,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1749,10 +1237,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1760,10 +1248,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1771,10 +1259,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1782,10 +1270,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -1793,10 +1281,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1804,10 +1292,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1815,10 +1303,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1826,10 +1314,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1837,10 +1325,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1848,10 +1336,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1859,18 +1347,51 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
     </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B60" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B60" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"HSE Required,Additional Training"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1881,8 +1402,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1895,30 +1416,30 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="D2">
         <f>IF(A2="","",COUNTIF(Workers!B:B,A2))</f>
@@ -1927,17 +1448,17 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="D3">
         <f>IF(A3="","",COUNTIF(Workers!B:B,A3))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2230,8 +1751,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2248,292 +1769,316 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" t="s">
+        <v>80</v>
+      </c>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" t="s">
+        <v>80</v>
+      </c>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F29" s="7"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F32" s="7"/>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.25">
@@ -3042,153 +2587,192 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C200" xr:uid="{00000000-0002-0000-0400-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C200" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>JobTitleOptions</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D1:D1048576" xr:uid="{E628E4CB-0312-4BE9-B69B-568FDF3593BC}">
+    <dataValidation type="list" allowBlank="1" sqref="D1:D1048576" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"active,inactive,onboarding,terminated"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{1970F7C8-85BA-47C1-B4B1-69516782C7FD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{00000000-0002-0000-0300-000002000000}">
       <formula1>ContractorOption</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Z200"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:AC200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="19" width="14" customWidth="1"/>
-    <col min="20" max="26" width="13" customWidth="1"/>
+    <col min="20" max="29" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
-      <c r="C1" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
-    </row>
-    <row r="2" spans="1:26" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+    </row>
+    <row r="2" spans="1:29" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <f>Certifications!A2</f>
+        <v>Protección Contra Caídas</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <f>Certifications!A3</f>
+        <v>Flama Expuesta</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f>Certifications!A4</f>
+        <v>Espacios Confinados</v>
+      </c>
+      <c r="F2" s="1" t="str">
+        <f>Certifications!A5</f>
+        <v>Manejo de Equipo Motorizado</v>
+      </c>
+      <c r="G2" s="1" t="str">
+        <f>Certifications!A6</f>
+        <v>Excavación o Zanja</v>
+      </c>
+      <c r="H2" s="1" t="str">
+        <f>Certifications!A7</f>
+        <v>Manejo de Tijeras (Scissor Lift)</v>
+      </c>
+      <c r="I2" s="1" t="str">
+        <f>Certifications!A8</f>
+        <v>Seguridad Eléctrica</v>
+      </c>
+      <c r="J2" s="1" t="str">
+        <f>Certifications!A9</f>
+        <v>Lockout</v>
+      </c>
+      <c r="K2" s="1" t="str">
+        <f>Certifications!A10</f>
+        <v>Manejo de Grúas</v>
+      </c>
+      <c r="L2" s="1" t="str">
+        <f>Certifications!A11</f>
+        <v>Escaleras</v>
+      </c>
+      <c r="M2" s="1" t="str">
+        <f>Certifications!A12</f>
+        <v>Andamios</v>
+      </c>
+      <c r="N2" s="1" t="str">
+        <f>Certifications!A13</f>
+        <v>Trabajos con Plomo o Asbesto</v>
+      </c>
+      <c r="O2" s="1" t="str">
+        <f>Certifications!A14</f>
+        <v>Comunicación de Riesgos</v>
+      </c>
+      <c r="P2" s="1" t="str">
+        <f>Certifications!A15</f>
+        <v>Inducción Jacobs/Lilly</v>
+      </c>
+      <c r="Q2" s="1" t="str">
+        <f>Certifications!A16</f>
+        <v>OSHA 40Hr HAZWOPER</v>
+      </c>
+      <c r="R2" s="1" t="str">
+        <f>Certifications!A17</f>
+        <v>OSHA 8Hr Refresher</v>
+      </c>
+      <c r="S2" s="1" t="str">
+        <f>Certifications!A18</f>
+        <v>Drilling Safety</v>
+      </c>
+      <c r="T2" s="1" t="str">
+        <f>Certifications!A19</f>
+        <v>Utility Locating</v>
+      </c>
+      <c r="U2" s="1" t="str">
+        <f>Certifications!A20</f>
+        <v>OSHA 10</v>
+      </c>
+      <c r="V2" s="1" t="str">
+        <f>Certifications!A21</f>
+        <v>OSHA 30</v>
+      </c>
+      <c r="W2" s="1" t="str">
+        <f>Certifications!A22</f>
+        <v>Rebar Safety</v>
+      </c>
+      <c r="X2" s="1" t="str">
+        <f>Certifications!A23</f>
+        <v>Formwork &amp; Shoring</v>
+      </c>
+      <c r="Y2" s="1" t="str">
+        <f>Certifications!A24</f>
+        <v>Silica Exposure</v>
+      </c>
+      <c r="Z2" s="1" t="str">
+        <f>Certifications!A25</f>
+        <v>Concrete &amp; Masonry</v>
+      </c>
+      <c r="AA2" s="1" t="str">
+        <f>Certifications!A26</f>
+        <v>Equipment Training</v>
+      </c>
+      <c r="AB2" s="1" t="str">
+        <f>Certifications!A27</f>
+        <v>OSHA 30 501</v>
+      </c>
+      <c r="AC2" s="1" t="str">
+        <f>Certifications!A28</f>
+        <v>OSHA 30 511</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="U2" s="1" t="s">
+      <c r="B3" t="s">
         <v>78</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
       </c>
       <c r="C3" s="9">
         <v>45764</v>
@@ -3228,13 +2812,16 @@
       <c r="X3" s="9"/>
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="C4" s="9">
         <v>45764</v>
@@ -3276,13 +2863,16 @@
       <c r="X4" s="9"/>
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="C5" s="9">
         <v>45764</v>
@@ -3324,13 +2914,16 @@
       <c r="X5" s="9"/>
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C6" s="9">
         <v>45764</v>
@@ -3370,13 +2963,16 @@
       <c r="X6" s="9"/>
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="C7" s="9">
         <v>45764</v>
@@ -3416,13 +3012,16 @@
       <c r="X7" s="9"/>
       <c r="Y7" s="9"/>
       <c r="Z7" s="9"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="C8" s="9">
         <v>45764</v>
@@ -3462,13 +3061,16 @@
       <c r="X8" s="9"/>
       <c r="Y8" s="9"/>
       <c r="Z8" s="9"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="C9" s="9">
         <v>46091</v>
@@ -3510,13 +3112,16 @@
       <c r="X9" s="9"/>
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA9" s="9"/>
+      <c r="AB9" s="9"/>
+      <c r="AC9" s="9"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="C10" s="9">
         <v>46091</v>
@@ -3558,13 +3163,16 @@
       <c r="X10" s="9"/>
       <c r="Y10" s="9"/>
       <c r="Z10" s="9"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA10" s="9"/>
+      <c r="AB10" s="9"/>
+      <c r="AC10" s="9"/>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="C11" s="9">
         <v>46091</v>
@@ -3573,7 +3181,6 @@
       <c r="E11" s="9">
         <v>46091</v>
       </c>
-      <c r="F11" s="9"/>
       <c r="G11" s="9">
         <v>46091</v>
       </c>
@@ -3606,13 +3213,16 @@
       <c r="X11" s="9"/>
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA11" s="9"/>
+      <c r="AB11" s="9"/>
+      <c r="AC11" s="9"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="C12" s="9">
         <v>46091</v>
@@ -3654,13 +3264,16 @@
       <c r="X12" s="9"/>
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="C13" s="9">
         <v>46091</v>
@@ -3702,13 +3315,16 @@
       <c r="X13" s="9"/>
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA13" s="9"/>
+      <c r="AB13" s="9"/>
+      <c r="AC13" s="9"/>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="C14" s="9">
         <v>46091</v>
@@ -3766,13 +3382,16 @@
       <c r="Z14" s="9">
         <v>44972</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA14" s="9"/>
+      <c r="AB14" s="9"/>
+      <c r="AC14" s="9"/>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="C15" s="9">
         <v>46091</v>
@@ -3830,13 +3449,16 @@
       <c r="Z15" s="9">
         <v>44972</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA15" s="9"/>
+      <c r="AB15" s="9"/>
+      <c r="AC15" s="9"/>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C16" s="9">
         <v>46091</v>
@@ -3894,8 +3516,17 @@
       <c r="Z16" s="9">
         <v>44972</v>
       </c>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA16" s="9"/>
+      <c r="AB16" s="9"/>
+      <c r="AC16" s="9"/>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
@@ -3909,7 +3540,9 @@
       <c r="M17" s="9"/>
       <c r="N17" s="9"/>
       <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
+      <c r="P17" s="9">
+        <v>46136</v>
+      </c>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
@@ -3920,34 +3553,62 @@
       <c r="X17" s="9"/>
       <c r="Y17" s="9"/>
       <c r="Z17" s="9"/>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA17" s="9"/>
+      <c r="AB17" s="9">
+        <v>45085</v>
+      </c>
+      <c r="AC17" s="9">
+        <v>44966</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" t="s">
+        <v>95</v>
+      </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="F18" s="9">
+        <v>46059</v>
+      </c>
       <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
+      <c r="H18" s="9">
+        <v>46059</v>
+      </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
+      <c r="K18" s="9">
+        <v>46059</v>
+      </c>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
+      <c r="P18" s="9">
+        <v>46136</v>
+      </c>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
       <c r="T18" s="9"/>
-      <c r="U18" s="9"/>
+      <c r="U18" s="9">
+        <v>46341</v>
+      </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
       <c r="X18" s="9"/>
       <c r="Y18" s="9"/>
       <c r="Z18" s="9"/>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA18" s="9">
+        <v>46059</v>
+      </c>
+      <c r="AB18" s="9"/>
+      <c r="AC18" s="9"/>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
@@ -3972,8 +3633,11 @@
       <c r="X19" s="9"/>
       <c r="Y19" s="9"/>
       <c r="Z19" s="9"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA19" s="9"/>
+      <c r="AB19" s="9"/>
+      <c r="AC19" s="9"/>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
@@ -3998,8 +3662,11 @@
       <c r="X20" s="9"/>
       <c r="Y20" s="9"/>
       <c r="Z20" s="9"/>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA20" s="9"/>
+      <c r="AB20" s="9"/>
+      <c r="AC20" s="9"/>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
@@ -4024,8 +3691,11 @@
       <c r="X21" s="9"/>
       <c r="Y21" s="9"/>
       <c r="Z21" s="9"/>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA21" s="9"/>
+      <c r="AB21" s="9"/>
+      <c r="AC21" s="9"/>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
@@ -4050,8 +3720,11 @@
       <c r="X22" s="9"/>
       <c r="Y22" s="9"/>
       <c r="Z22" s="9"/>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
@@ -4076,8 +3749,11 @@
       <c r="X23" s="9"/>
       <c r="Y23" s="9"/>
       <c r="Z23" s="9"/>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
@@ -4102,8 +3778,11 @@
       <c r="X24" s="9"/>
       <c r="Y24" s="9"/>
       <c r="Z24" s="9"/>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA24" s="9"/>
+      <c r="AB24" s="9"/>
+      <c r="AC24" s="9"/>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
@@ -4128,8 +3807,11 @@
       <c r="X25" s="9"/>
       <c r="Y25" s="9"/>
       <c r="Z25" s="9"/>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA25" s="9"/>
+      <c r="AB25" s="9"/>
+      <c r="AC25" s="9"/>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
@@ -4154,8 +3836,11 @@
       <c r="X26" s="9"/>
       <c r="Y26" s="9"/>
       <c r="Z26" s="9"/>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
@@ -4180,8 +3865,11 @@
       <c r="X27" s="9"/>
       <c r="Y27" s="9"/>
       <c r="Z27" s="9"/>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
@@ -4206,8 +3894,11 @@
       <c r="X28" s="9"/>
       <c r="Y28" s="9"/>
       <c r="Z28" s="9"/>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
@@ -4232,8 +3923,11 @@
       <c r="X29" s="9"/>
       <c r="Y29" s="9"/>
       <c r="Z29" s="9"/>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA29" s="9"/>
+      <c r="AB29" s="9"/>
+      <c r="AC29" s="9"/>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
@@ -4258,8 +3952,11 @@
       <c r="X30" s="9"/>
       <c r="Y30" s="9"/>
       <c r="Z30" s="9"/>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA30" s="9"/>
+      <c r="AB30" s="9"/>
+      <c r="AC30" s="9"/>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
@@ -4284,8 +3981,11 @@
       <c r="X31" s="9"/>
       <c r="Y31" s="9"/>
       <c r="Z31" s="9"/>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA31" s="9"/>
+      <c r="AB31" s="9"/>
+      <c r="AC31" s="9"/>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
@@ -4310,8 +4010,11 @@
       <c r="X32" s="9"/>
       <c r="Y32" s="9"/>
       <c r="Z32" s="9"/>
-    </row>
-    <row r="33" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA32" s="9"/>
+      <c r="AB32" s="9"/>
+      <c r="AC32" s="9"/>
+    </row>
+    <row r="33" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
@@ -4336,8 +4039,11 @@
       <c r="X33" s="9"/>
       <c r="Y33" s="9"/>
       <c r="Z33" s="9"/>
-    </row>
-    <row r="34" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA33" s="9"/>
+      <c r="AB33" s="9"/>
+      <c r="AC33" s="9"/>
+    </row>
+    <row r="34" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
@@ -4362,8 +4068,11 @@
       <c r="X34" s="9"/>
       <c r="Y34" s="9"/>
       <c r="Z34" s="9"/>
-    </row>
-    <row r="35" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA34" s="9"/>
+      <c r="AB34" s="9"/>
+      <c r="AC34" s="9"/>
+    </row>
+    <row r="35" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
@@ -4388,8 +4097,11 @@
       <c r="X35" s="9"/>
       <c r="Y35" s="9"/>
       <c r="Z35" s="9"/>
-    </row>
-    <row r="36" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA35" s="9"/>
+      <c r="AB35" s="9"/>
+      <c r="AC35" s="9"/>
+    </row>
+    <row r="36" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
@@ -4414,8 +4126,11 @@
       <c r="X36" s="9"/>
       <c r="Y36" s="9"/>
       <c r="Z36" s="9"/>
-    </row>
-    <row r="37" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA36" s="9"/>
+      <c r="AB36" s="9"/>
+      <c r="AC36" s="9"/>
+    </row>
+    <row r="37" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
@@ -4440,8 +4155,11 @@
       <c r="X37" s="9"/>
       <c r="Y37" s="9"/>
       <c r="Z37" s="9"/>
-    </row>
-    <row r="38" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA37" s="9"/>
+      <c r="AB37" s="9"/>
+      <c r="AC37" s="9"/>
+    </row>
+    <row r="38" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
@@ -4466,8 +4184,11 @@
       <c r="X38" s="9"/>
       <c r="Y38" s="9"/>
       <c r="Z38" s="9"/>
-    </row>
-    <row r="39" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA38" s="9"/>
+      <c r="AB38" s="9"/>
+      <c r="AC38" s="9"/>
+    </row>
+    <row r="39" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
@@ -4492,8 +4213,11 @@
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
       <c r="Z39" s="9"/>
-    </row>
-    <row r="40" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA39" s="9"/>
+      <c r="AB39" s="9"/>
+      <c r="AC39" s="9"/>
+    </row>
+    <row r="40" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
@@ -4518,8 +4242,11 @@
       <c r="X40" s="9"/>
       <c r="Y40" s="9"/>
       <c r="Z40" s="9"/>
-    </row>
-    <row r="41" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA40" s="9"/>
+      <c r="AB40" s="9"/>
+      <c r="AC40" s="9"/>
+    </row>
+    <row r="41" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
@@ -4544,8 +4271,11 @@
       <c r="X41" s="9"/>
       <c r="Y41" s="9"/>
       <c r="Z41" s="9"/>
-    </row>
-    <row r="42" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA41" s="9"/>
+      <c r="AB41" s="9"/>
+      <c r="AC41" s="9"/>
+    </row>
+    <row r="42" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
@@ -4570,8 +4300,11 @@
       <c r="X42" s="9"/>
       <c r="Y42" s="9"/>
       <c r="Z42" s="9"/>
-    </row>
-    <row r="43" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA42" s="9"/>
+      <c r="AB42" s="9"/>
+      <c r="AC42" s="9"/>
+    </row>
+    <row r="43" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
@@ -4596,8 +4329,11 @@
       <c r="X43" s="9"/>
       <c r="Y43" s="9"/>
       <c r="Z43" s="9"/>
-    </row>
-    <row r="44" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA43" s="9"/>
+      <c r="AB43" s="9"/>
+      <c r="AC43" s="9"/>
+    </row>
+    <row r="44" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
@@ -4622,8 +4358,11 @@
       <c r="X44" s="9"/>
       <c r="Y44" s="9"/>
       <c r="Z44" s="9"/>
-    </row>
-    <row r="45" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA44" s="9"/>
+      <c r="AB44" s="9"/>
+      <c r="AC44" s="9"/>
+    </row>
+    <row r="45" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
@@ -4648,8 +4387,11 @@
       <c r="X45" s="9"/>
       <c r="Y45" s="9"/>
       <c r="Z45" s="9"/>
-    </row>
-    <row r="46" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA45" s="9"/>
+      <c r="AB45" s="9"/>
+      <c r="AC45" s="9"/>
+    </row>
+    <row r="46" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
@@ -4674,8 +4416,11 @@
       <c r="X46" s="9"/>
       <c r="Y46" s="9"/>
       <c r="Z46" s="9"/>
-    </row>
-    <row r="47" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA46" s="9"/>
+      <c r="AB46" s="9"/>
+      <c r="AC46" s="9"/>
+    </row>
+    <row r="47" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
@@ -4700,8 +4445,11 @@
       <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
       <c r="Z47" s="9"/>
-    </row>
-    <row r="48" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA47" s="9"/>
+      <c r="AB47" s="9"/>
+      <c r="AC47" s="9"/>
+    </row>
+    <row r="48" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
@@ -4726,8 +4474,11 @@
       <c r="X48" s="9"/>
       <c r="Y48" s="9"/>
       <c r="Z48" s="9"/>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA48" s="9"/>
+      <c r="AB48" s="9"/>
+      <c r="AC48" s="9"/>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
@@ -4752,8 +4503,11 @@
       <c r="X49" s="9"/>
       <c r="Y49" s="9"/>
       <c r="Z49" s="9"/>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA49" s="9"/>
+      <c r="AB49" s="9"/>
+      <c r="AC49" s="9"/>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
@@ -4778,8 +4532,11 @@
       <c r="X50" s="9"/>
       <c r="Y50" s="9"/>
       <c r="Z50" s="9"/>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA50" s="9"/>
+      <c r="AB50" s="9"/>
+      <c r="AC50" s="9"/>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
@@ -4804,8 +4561,11 @@
       <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
       <c r="Z51" s="9"/>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA51" s="9"/>
+      <c r="AB51" s="9"/>
+      <c r="AC51" s="9"/>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
@@ -4830,8 +4590,11 @@
       <c r="X52" s="9"/>
       <c r="Y52" s="9"/>
       <c r="Z52" s="9"/>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA52" s="9"/>
+      <c r="AB52" s="9"/>
+      <c r="AC52" s="9"/>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
@@ -4856,8 +4619,11 @@
       <c r="X53" s="9"/>
       <c r="Y53" s="9"/>
       <c r="Z53" s="9"/>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA53" s="9"/>
+      <c r="AB53" s="9"/>
+      <c r="AC53" s="9"/>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
@@ -4882,8 +4648,11 @@
       <c r="X54" s="9"/>
       <c r="Y54" s="9"/>
       <c r="Z54" s="9"/>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA54" s="9"/>
+      <c r="AB54" s="9"/>
+      <c r="AC54" s="9"/>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
@@ -4908,8 +4677,11 @@
       <c r="X55" s="9"/>
       <c r="Y55" s="9"/>
       <c r="Z55" s="9"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA55" s="9"/>
+      <c r="AB55" s="9"/>
+      <c r="AC55" s="9"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
@@ -4934,8 +4706,11 @@
       <c r="X56" s="9"/>
       <c r="Y56" s="9"/>
       <c r="Z56" s="9"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA56" s="9"/>
+      <c r="AB56" s="9"/>
+      <c r="AC56" s="9"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
@@ -4960,8 +4735,11 @@
       <c r="X57" s="9"/>
       <c r="Y57" s="9"/>
       <c r="Z57" s="9"/>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA57" s="9"/>
+      <c r="AB57" s="9"/>
+      <c r="AC57" s="9"/>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
@@ -4986,8 +4764,11 @@
       <c r="X58" s="9"/>
       <c r="Y58" s="9"/>
       <c r="Z58" s="9"/>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA58" s="9"/>
+      <c r="AB58" s="9"/>
+      <c r="AC58" s="9"/>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
@@ -5012,8 +4793,11 @@
       <c r="X59" s="9"/>
       <c r="Y59" s="9"/>
       <c r="Z59" s="9"/>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA59" s="9"/>
+      <c r="AB59" s="9"/>
+      <c r="AC59" s="9"/>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
@@ -5038,8 +4822,11 @@
       <c r="X60" s="9"/>
       <c r="Y60" s="9"/>
       <c r="Z60" s="9"/>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA60" s="9"/>
+      <c r="AB60" s="9"/>
+      <c r="AC60" s="9"/>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
@@ -5064,8 +4851,11 @@
       <c r="X61" s="9"/>
       <c r="Y61" s="9"/>
       <c r="Z61" s="9"/>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA61" s="9"/>
+      <c r="AB61" s="9"/>
+      <c r="AC61" s="9"/>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
       <c r="E62" s="9"/>
@@ -5090,8 +4880,11 @@
       <c r="X62" s="9"/>
       <c r="Y62" s="9"/>
       <c r="Z62" s="9"/>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA62" s="9"/>
+      <c r="AB62" s="9"/>
+      <c r="AC62" s="9"/>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
@@ -5116,8 +4909,11 @@
       <c r="X63" s="9"/>
       <c r="Y63" s="9"/>
       <c r="Z63" s="9"/>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA63" s="9"/>
+      <c r="AB63" s="9"/>
+      <c r="AC63" s="9"/>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
@@ -5142,8 +4938,11 @@
       <c r="X64" s="9"/>
       <c r="Y64" s="9"/>
       <c r="Z64" s="9"/>
-    </row>
-    <row r="65" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA64" s="9"/>
+      <c r="AB64" s="9"/>
+      <c r="AC64" s="9"/>
+    </row>
+    <row r="65" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
       <c r="E65" s="9"/>
@@ -5168,8 +4967,11 @@
       <c r="X65" s="9"/>
       <c r="Y65" s="9"/>
       <c r="Z65" s="9"/>
-    </row>
-    <row r="66" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA65" s="9"/>
+      <c r="AB65" s="9"/>
+      <c r="AC65" s="9"/>
+    </row>
+    <row r="66" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
@@ -5194,8 +4996,11 @@
       <c r="X66" s="9"/>
       <c r="Y66" s="9"/>
       <c r="Z66" s="9"/>
-    </row>
-    <row r="67" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA66" s="9"/>
+      <c r="AB66" s="9"/>
+      <c r="AC66" s="9"/>
+    </row>
+    <row r="67" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
@@ -5220,8 +5025,11 @@
       <c r="X67" s="9"/>
       <c r="Y67" s="9"/>
       <c r="Z67" s="9"/>
-    </row>
-    <row r="68" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA67" s="9"/>
+      <c r="AB67" s="9"/>
+      <c r="AC67" s="9"/>
+    </row>
+    <row r="68" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
       <c r="E68" s="9"/>
@@ -5246,8 +5054,11 @@
       <c r="X68" s="9"/>
       <c r="Y68" s="9"/>
       <c r="Z68" s="9"/>
-    </row>
-    <row r="69" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA68" s="9"/>
+      <c r="AB68" s="9"/>
+      <c r="AC68" s="9"/>
+    </row>
+    <row r="69" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
@@ -5272,8 +5083,11 @@
       <c r="X69" s="9"/>
       <c r="Y69" s="9"/>
       <c r="Z69" s="9"/>
-    </row>
-    <row r="70" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA69" s="9"/>
+      <c r="AB69" s="9"/>
+      <c r="AC69" s="9"/>
+    </row>
+    <row r="70" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
@@ -5298,8 +5112,11 @@
       <c r="X70" s="9"/>
       <c r="Y70" s="9"/>
       <c r="Z70" s="9"/>
-    </row>
-    <row r="71" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA70" s="9"/>
+      <c r="AB70" s="9"/>
+      <c r="AC70" s="9"/>
+    </row>
+    <row r="71" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
@@ -5324,8 +5141,11 @@
       <c r="X71" s="9"/>
       <c r="Y71" s="9"/>
       <c r="Z71" s="9"/>
-    </row>
-    <row r="72" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA71" s="9"/>
+      <c r="AB71" s="9"/>
+      <c r="AC71" s="9"/>
+    </row>
+    <row r="72" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
@@ -5350,8 +5170,11 @@
       <c r="X72" s="9"/>
       <c r="Y72" s="9"/>
       <c r="Z72" s="9"/>
-    </row>
-    <row r="73" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA72" s="9"/>
+      <c r="AB72" s="9"/>
+      <c r="AC72" s="9"/>
+    </row>
+    <row r="73" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
@@ -5376,8 +5199,11 @@
       <c r="X73" s="9"/>
       <c r="Y73" s="9"/>
       <c r="Z73" s="9"/>
-    </row>
-    <row r="74" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA73" s="9"/>
+      <c r="AB73" s="9"/>
+      <c r="AC73" s="9"/>
+    </row>
+    <row r="74" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
@@ -5402,8 +5228,11 @@
       <c r="X74" s="9"/>
       <c r="Y74" s="9"/>
       <c r="Z74" s="9"/>
-    </row>
-    <row r="75" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA74" s="9"/>
+      <c r="AB74" s="9"/>
+      <c r="AC74" s="9"/>
+    </row>
+    <row r="75" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
@@ -5428,8 +5257,11 @@
       <c r="X75" s="9"/>
       <c r="Y75" s="9"/>
       <c r="Z75" s="9"/>
-    </row>
-    <row r="76" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA75" s="9"/>
+      <c r="AB75" s="9"/>
+      <c r="AC75" s="9"/>
+    </row>
+    <row r="76" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
@@ -5454,8 +5286,11 @@
       <c r="X76" s="9"/>
       <c r="Y76" s="9"/>
       <c r="Z76" s="9"/>
-    </row>
-    <row r="77" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA76" s="9"/>
+      <c r="AB76" s="9"/>
+      <c r="AC76" s="9"/>
+    </row>
+    <row r="77" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
@@ -5480,8 +5315,11 @@
       <c r="X77" s="9"/>
       <c r="Y77" s="9"/>
       <c r="Z77" s="9"/>
-    </row>
-    <row r="78" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA77" s="9"/>
+      <c r="AB77" s="9"/>
+      <c r="AC77" s="9"/>
+    </row>
+    <row r="78" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
@@ -5506,8 +5344,11 @@
       <c r="X78" s="9"/>
       <c r="Y78" s="9"/>
       <c r="Z78" s="9"/>
-    </row>
-    <row r="79" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA78" s="9"/>
+      <c r="AB78" s="9"/>
+      <c r="AC78" s="9"/>
+    </row>
+    <row r="79" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
@@ -5532,8 +5373,11 @@
       <c r="X79" s="9"/>
       <c r="Y79" s="9"/>
       <c r="Z79" s="9"/>
-    </row>
-    <row r="80" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA79" s="9"/>
+      <c r="AB79" s="9"/>
+      <c r="AC79" s="9"/>
+    </row>
+    <row r="80" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
@@ -5558,8 +5402,11 @@
       <c r="X80" s="9"/>
       <c r="Y80" s="9"/>
       <c r="Z80" s="9"/>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA80" s="9"/>
+      <c r="AB80" s="9"/>
+      <c r="AC80" s="9"/>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
       <c r="E81" s="9"/>
@@ -5584,8 +5431,11 @@
       <c r="X81" s="9"/>
       <c r="Y81" s="9"/>
       <c r="Z81" s="9"/>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA81" s="9"/>
+      <c r="AB81" s="9"/>
+      <c r="AC81" s="9"/>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
       <c r="E82" s="9"/>
@@ -5610,8 +5460,11 @@
       <c r="X82" s="9"/>
       <c r="Y82" s="9"/>
       <c r="Z82" s="9"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA82" s="9"/>
+      <c r="AB82" s="9"/>
+      <c r="AC82" s="9"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
       <c r="E83" s="9"/>
@@ -5636,8 +5489,11 @@
       <c r="X83" s="9"/>
       <c r="Y83" s="9"/>
       <c r="Z83" s="9"/>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA83" s="9"/>
+      <c r="AB83" s="9"/>
+      <c r="AC83" s="9"/>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
       <c r="E84" s="9"/>
@@ -5662,8 +5518,11 @@
       <c r="X84" s="9"/>
       <c r="Y84" s="9"/>
       <c r="Z84" s="9"/>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA84" s="9"/>
+      <c r="AB84" s="9"/>
+      <c r="AC84" s="9"/>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
       <c r="E85" s="9"/>
@@ -5688,8 +5547,11 @@
       <c r="X85" s="9"/>
       <c r="Y85" s="9"/>
       <c r="Z85" s="9"/>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA85" s="9"/>
+      <c r="AB85" s="9"/>
+      <c r="AC85" s="9"/>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
       <c r="E86" s="9"/>
@@ -5714,8 +5576,11 @@
       <c r="X86" s="9"/>
       <c r="Y86" s="9"/>
       <c r="Z86" s="9"/>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA86" s="9"/>
+      <c r="AB86" s="9"/>
+      <c r="AC86" s="9"/>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
       <c r="E87" s="9"/>
@@ -5740,8 +5605,11 @@
       <c r="X87" s="9"/>
       <c r="Y87" s="9"/>
       <c r="Z87" s="9"/>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA87" s="9"/>
+      <c r="AB87" s="9"/>
+      <c r="AC87" s="9"/>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
       <c r="E88" s="9"/>
@@ -5766,8 +5634,11 @@
       <c r="X88" s="9"/>
       <c r="Y88" s="9"/>
       <c r="Z88" s="9"/>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA88" s="9"/>
+      <c r="AB88" s="9"/>
+      <c r="AC88" s="9"/>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
       <c r="E89" s="9"/>
@@ -5792,8 +5663,11 @@
       <c r="X89" s="9"/>
       <c r="Y89" s="9"/>
       <c r="Z89" s="9"/>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA89" s="9"/>
+      <c r="AB89" s="9"/>
+      <c r="AC89" s="9"/>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
       <c r="E90" s="9"/>
@@ -5818,8 +5692,11 @@
       <c r="X90" s="9"/>
       <c r="Y90" s="9"/>
       <c r="Z90" s="9"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA90" s="9"/>
+      <c r="AB90" s="9"/>
+      <c r="AC90" s="9"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
       <c r="E91" s="9"/>
@@ -5844,8 +5721,11 @@
       <c r="X91" s="9"/>
       <c r="Y91" s="9"/>
       <c r="Z91" s="9"/>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA91" s="9"/>
+      <c r="AB91" s="9"/>
+      <c r="AC91" s="9"/>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
       <c r="E92" s="9"/>
@@ -5870,8 +5750,11 @@
       <c r="X92" s="9"/>
       <c r="Y92" s="9"/>
       <c r="Z92" s="9"/>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA92" s="9"/>
+      <c r="AB92" s="9"/>
+      <c r="AC92" s="9"/>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
       <c r="E93" s="9"/>
@@ -5896,8 +5779,11 @@
       <c r="X93" s="9"/>
       <c r="Y93" s="9"/>
       <c r="Z93" s="9"/>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA93" s="9"/>
+      <c r="AB93" s="9"/>
+      <c r="AC93" s="9"/>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
       <c r="E94" s="9"/>
@@ -5922,8 +5808,11 @@
       <c r="X94" s="9"/>
       <c r="Y94" s="9"/>
       <c r="Z94" s="9"/>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA94" s="9"/>
+      <c r="AB94" s="9"/>
+      <c r="AC94" s="9"/>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
@@ -5948,8 +5837,11 @@
       <c r="X95" s="9"/>
       <c r="Y95" s="9"/>
       <c r="Z95" s="9"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA95" s="9"/>
+      <c r="AB95" s="9"/>
+      <c r="AC95" s="9"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
       <c r="E96" s="9"/>
@@ -5974,8 +5866,11 @@
       <c r="X96" s="9"/>
       <c r="Y96" s="9"/>
       <c r="Z96" s="9"/>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA96" s="9"/>
+      <c r="AB96" s="9"/>
+      <c r="AC96" s="9"/>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
       <c r="E97" s="9"/>
@@ -6000,8 +5895,11 @@
       <c r="X97" s="9"/>
       <c r="Y97" s="9"/>
       <c r="Z97" s="9"/>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA97" s="9"/>
+      <c r="AB97" s="9"/>
+      <c r="AC97" s="9"/>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
       <c r="E98" s="9"/>
@@ -6026,8 +5924,11 @@
       <c r="X98" s="9"/>
       <c r="Y98" s="9"/>
       <c r="Z98" s="9"/>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA98" s="9"/>
+      <c r="AB98" s="9"/>
+      <c r="AC98" s="9"/>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
@@ -6052,8 +5953,11 @@
       <c r="X99" s="9"/>
       <c r="Y99" s="9"/>
       <c r="Z99" s="9"/>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA99" s="9"/>
+      <c r="AB99" s="9"/>
+      <c r="AC99" s="9"/>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
       <c r="E100" s="9"/>
@@ -6078,8 +5982,11 @@
       <c r="X100" s="9"/>
       <c r="Y100" s="9"/>
       <c r="Z100" s="9"/>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA100" s="9"/>
+      <c r="AB100" s="9"/>
+      <c r="AC100" s="9"/>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
       <c r="E101" s="9"/>
@@ -6104,8 +6011,11 @@
       <c r="X101" s="9"/>
       <c r="Y101" s="9"/>
       <c r="Z101" s="9"/>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA101" s="9"/>
+      <c r="AB101" s="9"/>
+      <c r="AC101" s="9"/>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
       <c r="E102" s="9"/>
@@ -6130,8 +6040,11 @@
       <c r="X102" s="9"/>
       <c r="Y102" s="9"/>
       <c r="Z102" s="9"/>
-    </row>
-    <row r="103" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA102" s="9"/>
+      <c r="AB102" s="9"/>
+      <c r="AC102" s="9"/>
+    </row>
+    <row r="103" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
       <c r="E103" s="9"/>
@@ -6156,8 +6069,11 @@
       <c r="X103" s="9"/>
       <c r="Y103" s="9"/>
       <c r="Z103" s="9"/>
-    </row>
-    <row r="104" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA103" s="9"/>
+      <c r="AB103" s="9"/>
+      <c r="AC103" s="9"/>
+    </row>
+    <row r="104" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C104" s="9"/>
       <c r="D104" s="9"/>
       <c r="E104" s="9"/>
@@ -6182,8 +6098,11 @@
       <c r="X104" s="9"/>
       <c r="Y104" s="9"/>
       <c r="Z104" s="9"/>
-    </row>
-    <row r="105" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA104" s="9"/>
+      <c r="AB104" s="9"/>
+      <c r="AC104" s="9"/>
+    </row>
+    <row r="105" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C105" s="9"/>
       <c r="D105" s="9"/>
       <c r="E105" s="9"/>
@@ -6208,8 +6127,11 @@
       <c r="X105" s="9"/>
       <c r="Y105" s="9"/>
       <c r="Z105" s="9"/>
-    </row>
-    <row r="106" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA105" s="9"/>
+      <c r="AB105" s="9"/>
+      <c r="AC105" s="9"/>
+    </row>
+    <row r="106" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
       <c r="E106" s="9"/>
@@ -6234,8 +6156,11 @@
       <c r="X106" s="9"/>
       <c r="Y106" s="9"/>
       <c r="Z106" s="9"/>
-    </row>
-    <row r="107" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA106" s="9"/>
+      <c r="AB106" s="9"/>
+      <c r="AC106" s="9"/>
+    </row>
+    <row r="107" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
       <c r="E107" s="9"/>
@@ -6260,8 +6185,11 @@
       <c r="X107" s="9"/>
       <c r="Y107" s="9"/>
       <c r="Z107" s="9"/>
-    </row>
-    <row r="108" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA107" s="9"/>
+      <c r="AB107" s="9"/>
+      <c r="AC107" s="9"/>
+    </row>
+    <row r="108" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
       <c r="E108" s="9"/>
@@ -6286,8 +6214,11 @@
       <c r="X108" s="9"/>
       <c r="Y108" s="9"/>
       <c r="Z108" s="9"/>
-    </row>
-    <row r="109" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA108" s="9"/>
+      <c r="AB108" s="9"/>
+      <c r="AC108" s="9"/>
+    </row>
+    <row r="109" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
       <c r="E109" s="9"/>
@@ -6312,8 +6243,11 @@
       <c r="X109" s="9"/>
       <c r="Y109" s="9"/>
       <c r="Z109" s="9"/>
-    </row>
-    <row r="110" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA109" s="9"/>
+      <c r="AB109" s="9"/>
+      <c r="AC109" s="9"/>
+    </row>
+    <row r="110" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
       <c r="E110" s="9"/>
@@ -6338,8 +6272,11 @@
       <c r="X110" s="9"/>
       <c r="Y110" s="9"/>
       <c r="Z110" s="9"/>
-    </row>
-    <row r="111" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA110" s="9"/>
+      <c r="AB110" s="9"/>
+      <c r="AC110" s="9"/>
+    </row>
+    <row r="111" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
@@ -6364,8 +6301,11 @@
       <c r="X111" s="9"/>
       <c r="Y111" s="9"/>
       <c r="Z111" s="9"/>
-    </row>
-    <row r="112" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA111" s="9"/>
+      <c r="AB111" s="9"/>
+      <c r="AC111" s="9"/>
+    </row>
+    <row r="112" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
       <c r="E112" s="9"/>
@@ -6390,8 +6330,11 @@
       <c r="X112" s="9"/>
       <c r="Y112" s="9"/>
       <c r="Z112" s="9"/>
-    </row>
-    <row r="113" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA112" s="9"/>
+      <c r="AB112" s="9"/>
+      <c r="AC112" s="9"/>
+    </row>
+    <row r="113" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
       <c r="E113" s="9"/>
@@ -6416,8 +6359,11 @@
       <c r="X113" s="9"/>
       <c r="Y113" s="9"/>
       <c r="Z113" s="9"/>
-    </row>
-    <row r="114" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA113" s="9"/>
+      <c r="AB113" s="9"/>
+      <c r="AC113" s="9"/>
+    </row>
+    <row r="114" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
       <c r="E114" s="9"/>
@@ -6442,8 +6388,11 @@
       <c r="X114" s="9"/>
       <c r="Y114" s="9"/>
       <c r="Z114" s="9"/>
-    </row>
-    <row r="115" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA114" s="9"/>
+      <c r="AB114" s="9"/>
+      <c r="AC114" s="9"/>
+    </row>
+    <row r="115" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
       <c r="E115" s="9"/>
@@ -6468,8 +6417,11 @@
       <c r="X115" s="9"/>
       <c r="Y115" s="9"/>
       <c r="Z115" s="9"/>
-    </row>
-    <row r="116" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA115" s="9"/>
+      <c r="AB115" s="9"/>
+      <c r="AC115" s="9"/>
+    </row>
+    <row r="116" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
       <c r="E116" s="9"/>
@@ -6494,8 +6446,11 @@
       <c r="X116" s="9"/>
       <c r="Y116" s="9"/>
       <c r="Z116" s="9"/>
-    </row>
-    <row r="117" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA116" s="9"/>
+      <c r="AB116" s="9"/>
+      <c r="AC116" s="9"/>
+    </row>
+    <row r="117" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
       <c r="E117" s="9"/>
@@ -6520,8 +6475,11 @@
       <c r="X117" s="9"/>
       <c r="Y117" s="9"/>
       <c r="Z117" s="9"/>
-    </row>
-    <row r="118" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA117" s="9"/>
+      <c r="AB117" s="9"/>
+      <c r="AC117" s="9"/>
+    </row>
+    <row r="118" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
       <c r="E118" s="9"/>
@@ -6546,8 +6504,11 @@
       <c r="X118" s="9"/>
       <c r="Y118" s="9"/>
       <c r="Z118" s="9"/>
-    </row>
-    <row r="119" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA118" s="9"/>
+      <c r="AB118" s="9"/>
+      <c r="AC118" s="9"/>
+    </row>
+    <row r="119" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
       <c r="E119" s="9"/>
@@ -6572,8 +6533,11 @@
       <c r="X119" s="9"/>
       <c r="Y119" s="9"/>
       <c r="Z119" s="9"/>
-    </row>
-    <row r="120" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA119" s="9"/>
+      <c r="AB119" s="9"/>
+      <c r="AC119" s="9"/>
+    </row>
+    <row r="120" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
       <c r="E120" s="9"/>
@@ -6598,8 +6562,11 @@
       <c r="X120" s="9"/>
       <c r="Y120" s="9"/>
       <c r="Z120" s="9"/>
-    </row>
-    <row r="121" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA120" s="9"/>
+      <c r="AB120" s="9"/>
+      <c r="AC120" s="9"/>
+    </row>
+    <row r="121" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
       <c r="E121" s="9"/>
@@ -6624,8 +6591,11 @@
       <c r="X121" s="9"/>
       <c r="Y121" s="9"/>
       <c r="Z121" s="9"/>
-    </row>
-    <row r="122" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA121" s="9"/>
+      <c r="AB121" s="9"/>
+      <c r="AC121" s="9"/>
+    </row>
+    <row r="122" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
       <c r="E122" s="9"/>
@@ -6650,8 +6620,11 @@
       <c r="X122" s="9"/>
       <c r="Y122" s="9"/>
       <c r="Z122" s="9"/>
-    </row>
-    <row r="123" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA122" s="9"/>
+      <c r="AB122" s="9"/>
+      <c r="AC122" s="9"/>
+    </row>
+    <row r="123" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
       <c r="E123" s="9"/>
@@ -6676,8 +6649,11 @@
       <c r="X123" s="9"/>
       <c r="Y123" s="9"/>
       <c r="Z123" s="9"/>
-    </row>
-    <row r="124" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA123" s="9"/>
+      <c r="AB123" s="9"/>
+      <c r="AC123" s="9"/>
+    </row>
+    <row r="124" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
       <c r="E124" s="9"/>
@@ -6702,8 +6678,11 @@
       <c r="X124" s="9"/>
       <c r="Y124" s="9"/>
       <c r="Z124" s="9"/>
-    </row>
-    <row r="125" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA124" s="9"/>
+      <c r="AB124" s="9"/>
+      <c r="AC124" s="9"/>
+    </row>
+    <row r="125" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
       <c r="E125" s="9"/>
@@ -6728,8 +6707,11 @@
       <c r="X125" s="9"/>
       <c r="Y125" s="9"/>
       <c r="Z125" s="9"/>
-    </row>
-    <row r="126" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA125" s="9"/>
+      <c r="AB125" s="9"/>
+      <c r="AC125" s="9"/>
+    </row>
+    <row r="126" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
       <c r="E126" s="9"/>
@@ -6754,8 +6736,11 @@
       <c r="X126" s="9"/>
       <c r="Y126" s="9"/>
       <c r="Z126" s="9"/>
-    </row>
-    <row r="127" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA126" s="9"/>
+      <c r="AB126" s="9"/>
+      <c r="AC126" s="9"/>
+    </row>
+    <row r="127" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
       <c r="E127" s="9"/>
@@ -6780,8 +6765,11 @@
       <c r="X127" s="9"/>
       <c r="Y127" s="9"/>
       <c r="Z127" s="9"/>
-    </row>
-    <row r="128" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA127" s="9"/>
+      <c r="AB127" s="9"/>
+      <c r="AC127" s="9"/>
+    </row>
+    <row r="128" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
       <c r="E128" s="9"/>
@@ -6806,8 +6794,11 @@
       <c r="X128" s="9"/>
       <c r="Y128" s="9"/>
       <c r="Z128" s="9"/>
-    </row>
-    <row r="129" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA128" s="9"/>
+      <c r="AB128" s="9"/>
+      <c r="AC128" s="9"/>
+    </row>
+    <row r="129" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C129" s="9"/>
       <c r="D129" s="9"/>
       <c r="E129" s="9"/>
@@ -6832,8 +6823,11 @@
       <c r="X129" s="9"/>
       <c r="Y129" s="9"/>
       <c r="Z129" s="9"/>
-    </row>
-    <row r="130" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA129" s="9"/>
+      <c r="AB129" s="9"/>
+      <c r="AC129" s="9"/>
+    </row>
+    <row r="130" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C130" s="9"/>
       <c r="D130" s="9"/>
       <c r="E130" s="9"/>
@@ -6858,8 +6852,11 @@
       <c r="X130" s="9"/>
       <c r="Y130" s="9"/>
       <c r="Z130" s="9"/>
-    </row>
-    <row r="131" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA130" s="9"/>
+      <c r="AB130" s="9"/>
+      <c r="AC130" s="9"/>
+    </row>
+    <row r="131" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
       <c r="E131" s="9"/>
@@ -6884,8 +6881,11 @@
       <c r="X131" s="9"/>
       <c r="Y131" s="9"/>
       <c r="Z131" s="9"/>
-    </row>
-    <row r="132" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA131" s="9"/>
+      <c r="AB131" s="9"/>
+      <c r="AC131" s="9"/>
+    </row>
+    <row r="132" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C132" s="9"/>
       <c r="D132" s="9"/>
       <c r="E132" s="9"/>
@@ -6910,8 +6910,11 @@
       <c r="X132" s="9"/>
       <c r="Y132" s="9"/>
       <c r="Z132" s="9"/>
-    </row>
-    <row r="133" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA132" s="9"/>
+      <c r="AB132" s="9"/>
+      <c r="AC132" s="9"/>
+    </row>
+    <row r="133" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
       <c r="E133" s="9"/>
@@ -6936,8 +6939,11 @@
       <c r="X133" s="9"/>
       <c r="Y133" s="9"/>
       <c r="Z133" s="9"/>
-    </row>
-    <row r="134" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA133" s="9"/>
+      <c r="AB133" s="9"/>
+      <c r="AC133" s="9"/>
+    </row>
+    <row r="134" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
       <c r="E134" s="9"/>
@@ -6962,8 +6968,11 @@
       <c r="X134" s="9"/>
       <c r="Y134" s="9"/>
       <c r="Z134" s="9"/>
-    </row>
-    <row r="135" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA134" s="9"/>
+      <c r="AB134" s="9"/>
+      <c r="AC134" s="9"/>
+    </row>
+    <row r="135" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
       <c r="E135" s="9"/>
@@ -6988,8 +6997,11 @@
       <c r="X135" s="9"/>
       <c r="Y135" s="9"/>
       <c r="Z135" s="9"/>
-    </row>
-    <row r="136" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA135" s="9"/>
+      <c r="AB135" s="9"/>
+      <c r="AC135" s="9"/>
+    </row>
+    <row r="136" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C136" s="9"/>
       <c r="D136" s="9"/>
       <c r="E136" s="9"/>
@@ -7014,8 +7026,11 @@
       <c r="X136" s="9"/>
       <c r="Y136" s="9"/>
       <c r="Z136" s="9"/>
-    </row>
-    <row r="137" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA136" s="9"/>
+      <c r="AB136" s="9"/>
+      <c r="AC136" s="9"/>
+    </row>
+    <row r="137" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
       <c r="E137" s="9"/>
@@ -7040,8 +7055,11 @@
       <c r="X137" s="9"/>
       <c r="Y137" s="9"/>
       <c r="Z137" s="9"/>
-    </row>
-    <row r="138" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA137" s="9"/>
+      <c r="AB137" s="9"/>
+      <c r="AC137" s="9"/>
+    </row>
+    <row r="138" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
       <c r="E138" s="9"/>
@@ -7066,8 +7084,11 @@
       <c r="X138" s="9"/>
       <c r="Y138" s="9"/>
       <c r="Z138" s="9"/>
-    </row>
-    <row r="139" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA138" s="9"/>
+      <c r="AB138" s="9"/>
+      <c r="AC138" s="9"/>
+    </row>
+    <row r="139" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
       <c r="E139" s="9"/>
@@ -7092,8 +7113,11 @@
       <c r="X139" s="9"/>
       <c r="Y139" s="9"/>
       <c r="Z139" s="9"/>
-    </row>
-    <row r="140" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA139" s="9"/>
+      <c r="AB139" s="9"/>
+      <c r="AC139" s="9"/>
+    </row>
+    <row r="140" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
       <c r="E140" s="9"/>
@@ -7118,8 +7142,11 @@
       <c r="X140" s="9"/>
       <c r="Y140" s="9"/>
       <c r="Z140" s="9"/>
-    </row>
-    <row r="141" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA140" s="9"/>
+      <c r="AB140" s="9"/>
+      <c r="AC140" s="9"/>
+    </row>
+    <row r="141" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
       <c r="E141" s="9"/>
@@ -7144,8 +7171,11 @@
       <c r="X141" s="9"/>
       <c r="Y141" s="9"/>
       <c r="Z141" s="9"/>
-    </row>
-    <row r="142" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA141" s="9"/>
+      <c r="AB141" s="9"/>
+      <c r="AC141" s="9"/>
+    </row>
+    <row r="142" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C142" s="9"/>
       <c r="D142" s="9"/>
       <c r="E142" s="9"/>
@@ -7170,8 +7200,11 @@
       <c r="X142" s="9"/>
       <c r="Y142" s="9"/>
       <c r="Z142" s="9"/>
-    </row>
-    <row r="143" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA142" s="9"/>
+      <c r="AB142" s="9"/>
+      <c r="AC142" s="9"/>
+    </row>
+    <row r="143" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C143" s="9"/>
       <c r="D143" s="9"/>
       <c r="E143" s="9"/>
@@ -7196,8 +7229,11 @@
       <c r="X143" s="9"/>
       <c r="Y143" s="9"/>
       <c r="Z143" s="9"/>
-    </row>
-    <row r="144" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA143" s="9"/>
+      <c r="AB143" s="9"/>
+      <c r="AC143" s="9"/>
+    </row>
+    <row r="144" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C144" s="9"/>
       <c r="D144" s="9"/>
       <c r="E144" s="9"/>
@@ -7222,8 +7258,11 @@
       <c r="X144" s="9"/>
       <c r="Y144" s="9"/>
       <c r="Z144" s="9"/>
-    </row>
-    <row r="145" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA144" s="9"/>
+      <c r="AB144" s="9"/>
+      <c r="AC144" s="9"/>
+    </row>
+    <row r="145" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C145" s="9"/>
       <c r="D145" s="9"/>
       <c r="E145" s="9"/>
@@ -7248,8 +7287,11 @@
       <c r="X145" s="9"/>
       <c r="Y145" s="9"/>
       <c r="Z145" s="9"/>
-    </row>
-    <row r="146" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA145" s="9"/>
+      <c r="AB145" s="9"/>
+      <c r="AC145" s="9"/>
+    </row>
+    <row r="146" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C146" s="9"/>
       <c r="D146" s="9"/>
       <c r="E146" s="9"/>
@@ -7274,8 +7316,11 @@
       <c r="X146" s="9"/>
       <c r="Y146" s="9"/>
       <c r="Z146" s="9"/>
-    </row>
-    <row r="147" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA146" s="9"/>
+      <c r="AB146" s="9"/>
+      <c r="AC146" s="9"/>
+    </row>
+    <row r="147" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C147" s="9"/>
       <c r="D147" s="9"/>
       <c r="E147" s="9"/>
@@ -7300,8 +7345,11 @@
       <c r="X147" s="9"/>
       <c r="Y147" s="9"/>
       <c r="Z147" s="9"/>
-    </row>
-    <row r="148" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA147" s="9"/>
+      <c r="AB147" s="9"/>
+      <c r="AC147" s="9"/>
+    </row>
+    <row r="148" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
       <c r="E148" s="9"/>
@@ -7326,8 +7374,11 @@
       <c r="X148" s="9"/>
       <c r="Y148" s="9"/>
       <c r="Z148" s="9"/>
-    </row>
-    <row r="149" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA148" s="9"/>
+      <c r="AB148" s="9"/>
+      <c r="AC148" s="9"/>
+    </row>
+    <row r="149" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C149" s="9"/>
       <c r="D149" s="9"/>
       <c r="E149" s="9"/>
@@ -7352,8 +7403,11 @@
       <c r="X149" s="9"/>
       <c r="Y149" s="9"/>
       <c r="Z149" s="9"/>
-    </row>
-    <row r="150" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA149" s="9"/>
+      <c r="AB149" s="9"/>
+      <c r="AC149" s="9"/>
+    </row>
+    <row r="150" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C150" s="9"/>
       <c r="D150" s="9"/>
       <c r="E150" s="9"/>
@@ -7378,8 +7432,11 @@
       <c r="X150" s="9"/>
       <c r="Y150" s="9"/>
       <c r="Z150" s="9"/>
-    </row>
-    <row r="151" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA150" s="9"/>
+      <c r="AB150" s="9"/>
+      <c r="AC150" s="9"/>
+    </row>
+    <row r="151" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
@@ -7404,8 +7461,11 @@
       <c r="X151" s="9"/>
       <c r="Y151" s="9"/>
       <c r="Z151" s="9"/>
-    </row>
-    <row r="152" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA151" s="9"/>
+      <c r="AB151" s="9"/>
+      <c r="AC151" s="9"/>
+    </row>
+    <row r="152" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
       <c r="E152" s="9"/>
@@ -7430,8 +7490,11 @@
       <c r="X152" s="9"/>
       <c r="Y152" s="9"/>
       <c r="Z152" s="9"/>
-    </row>
-    <row r="153" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA152" s="9"/>
+      <c r="AB152" s="9"/>
+      <c r="AC152" s="9"/>
+    </row>
+    <row r="153" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
       <c r="E153" s="9"/>
@@ -7456,8 +7519,11 @@
       <c r="X153" s="9"/>
       <c r="Y153" s="9"/>
       <c r="Z153" s="9"/>
-    </row>
-    <row r="154" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA153" s="9"/>
+      <c r="AB153" s="9"/>
+      <c r="AC153" s="9"/>
+    </row>
+    <row r="154" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
       <c r="E154" s="9"/>
@@ -7482,8 +7548,11 @@
       <c r="X154" s="9"/>
       <c r="Y154" s="9"/>
       <c r="Z154" s="9"/>
-    </row>
-    <row r="155" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA154" s="9"/>
+      <c r="AB154" s="9"/>
+      <c r="AC154" s="9"/>
+    </row>
+    <row r="155" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
       <c r="E155" s="9"/>
@@ -7508,8 +7577,11 @@
       <c r="X155" s="9"/>
       <c r="Y155" s="9"/>
       <c r="Z155" s="9"/>
-    </row>
-    <row r="156" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA155" s="9"/>
+      <c r="AB155" s="9"/>
+      <c r="AC155" s="9"/>
+    </row>
+    <row r="156" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
       <c r="E156" s="9"/>
@@ -7534,8 +7606,11 @@
       <c r="X156" s="9"/>
       <c r="Y156" s="9"/>
       <c r="Z156" s="9"/>
-    </row>
-    <row r="157" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA156" s="9"/>
+      <c r="AB156" s="9"/>
+      <c r="AC156" s="9"/>
+    </row>
+    <row r="157" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
       <c r="E157" s="9"/>
@@ -7560,8 +7635,11 @@
       <c r="X157" s="9"/>
       <c r="Y157" s="9"/>
       <c r="Z157" s="9"/>
-    </row>
-    <row r="158" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA157" s="9"/>
+      <c r="AB157" s="9"/>
+      <c r="AC157" s="9"/>
+    </row>
+    <row r="158" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
       <c r="E158" s="9"/>
@@ -7586,8 +7664,11 @@
       <c r="X158" s="9"/>
       <c r="Y158" s="9"/>
       <c r="Z158" s="9"/>
-    </row>
-    <row r="159" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA158" s="9"/>
+      <c r="AB158" s="9"/>
+      <c r="AC158" s="9"/>
+    </row>
+    <row r="159" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
       <c r="E159" s="9"/>
@@ -7612,8 +7693,11 @@
       <c r="X159" s="9"/>
       <c r="Y159" s="9"/>
       <c r="Z159" s="9"/>
-    </row>
-    <row r="160" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA159" s="9"/>
+      <c r="AB159" s="9"/>
+      <c r="AC159" s="9"/>
+    </row>
+    <row r="160" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
       <c r="E160" s="9"/>
@@ -7638,8 +7722,11 @@
       <c r="X160" s="9"/>
       <c r="Y160" s="9"/>
       <c r="Z160" s="9"/>
-    </row>
-    <row r="161" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA160" s="9"/>
+      <c r="AB160" s="9"/>
+      <c r="AC160" s="9"/>
+    </row>
+    <row r="161" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C161" s="9"/>
       <c r="D161" s="9"/>
       <c r="E161" s="9"/>
@@ -7664,8 +7751,11 @@
       <c r="X161" s="9"/>
       <c r="Y161" s="9"/>
       <c r="Z161" s="9"/>
-    </row>
-    <row r="162" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA161" s="9"/>
+      <c r="AB161" s="9"/>
+      <c r="AC161" s="9"/>
+    </row>
+    <row r="162" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C162" s="9"/>
       <c r="D162" s="9"/>
       <c r="E162" s="9"/>
@@ -7690,8 +7780,11 @@
       <c r="X162" s="9"/>
       <c r="Y162" s="9"/>
       <c r="Z162" s="9"/>
-    </row>
-    <row r="163" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA162" s="9"/>
+      <c r="AB162" s="9"/>
+      <c r="AC162" s="9"/>
+    </row>
+    <row r="163" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
@@ -7716,8 +7809,11 @@
       <c r="X163" s="9"/>
       <c r="Y163" s="9"/>
       <c r="Z163" s="9"/>
-    </row>
-    <row r="164" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA163" s="9"/>
+      <c r="AB163" s="9"/>
+      <c r="AC163" s="9"/>
+    </row>
+    <row r="164" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C164" s="9"/>
       <c r="D164" s="9"/>
       <c r="E164" s="9"/>
@@ -7742,8 +7838,11 @@
       <c r="X164" s="9"/>
       <c r="Y164" s="9"/>
       <c r="Z164" s="9"/>
-    </row>
-    <row r="165" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA164" s="9"/>
+      <c r="AB164" s="9"/>
+      <c r="AC164" s="9"/>
+    </row>
+    <row r="165" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C165" s="9"/>
       <c r="D165" s="9"/>
       <c r="E165" s="9"/>
@@ -7768,8 +7867,11 @@
       <c r="X165" s="9"/>
       <c r="Y165" s="9"/>
       <c r="Z165" s="9"/>
-    </row>
-    <row r="166" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA165" s="9"/>
+      <c r="AB165" s="9"/>
+      <c r="AC165" s="9"/>
+    </row>
+    <row r="166" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C166" s="9"/>
       <c r="D166" s="9"/>
       <c r="E166" s="9"/>
@@ -7794,8 +7896,11 @@
       <c r="X166" s="9"/>
       <c r="Y166" s="9"/>
       <c r="Z166" s="9"/>
-    </row>
-    <row r="167" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA166" s="9"/>
+      <c r="AB166" s="9"/>
+      <c r="AC166" s="9"/>
+    </row>
+    <row r="167" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C167" s="9"/>
       <c r="D167" s="9"/>
       <c r="E167" s="9"/>
@@ -7820,8 +7925,11 @@
       <c r="X167" s="9"/>
       <c r="Y167" s="9"/>
       <c r="Z167" s="9"/>
-    </row>
-    <row r="168" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA167" s="9"/>
+      <c r="AB167" s="9"/>
+      <c r="AC167" s="9"/>
+    </row>
+    <row r="168" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C168" s="9"/>
       <c r="D168" s="9"/>
       <c r="E168" s="9"/>
@@ -7846,8 +7954,11 @@
       <c r="X168" s="9"/>
       <c r="Y168" s="9"/>
       <c r="Z168" s="9"/>
-    </row>
-    <row r="169" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA168" s="9"/>
+      <c r="AB168" s="9"/>
+      <c r="AC168" s="9"/>
+    </row>
+    <row r="169" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C169" s="9"/>
       <c r="D169" s="9"/>
       <c r="E169" s="9"/>
@@ -7872,8 +7983,11 @@
       <c r="X169" s="9"/>
       <c r="Y169" s="9"/>
       <c r="Z169" s="9"/>
-    </row>
-    <row r="170" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA169" s="9"/>
+      <c r="AB169" s="9"/>
+      <c r="AC169" s="9"/>
+    </row>
+    <row r="170" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C170" s="9"/>
       <c r="D170" s="9"/>
       <c r="E170" s="9"/>
@@ -7898,8 +8012,11 @@
       <c r="X170" s="9"/>
       <c r="Y170" s="9"/>
       <c r="Z170" s="9"/>
-    </row>
-    <row r="171" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA170" s="9"/>
+      <c r="AB170" s="9"/>
+      <c r="AC170" s="9"/>
+    </row>
+    <row r="171" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C171" s="9"/>
       <c r="D171" s="9"/>
       <c r="E171" s="9"/>
@@ -7924,8 +8041,11 @@
       <c r="X171" s="9"/>
       <c r="Y171" s="9"/>
       <c r="Z171" s="9"/>
-    </row>
-    <row r="172" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA171" s="9"/>
+      <c r="AB171" s="9"/>
+      <c r="AC171" s="9"/>
+    </row>
+    <row r="172" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C172" s="9"/>
       <c r="D172" s="9"/>
       <c r="E172" s="9"/>
@@ -7950,8 +8070,11 @@
       <c r="X172" s="9"/>
       <c r="Y172" s="9"/>
       <c r="Z172" s="9"/>
-    </row>
-    <row r="173" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA172" s="9"/>
+      <c r="AB172" s="9"/>
+      <c r="AC172" s="9"/>
+    </row>
+    <row r="173" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C173" s="9"/>
       <c r="D173" s="9"/>
       <c r="E173" s="9"/>
@@ -7976,8 +8099,11 @@
       <c r="X173" s="9"/>
       <c r="Y173" s="9"/>
       <c r="Z173" s="9"/>
-    </row>
-    <row r="174" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA173" s="9"/>
+      <c r="AB173" s="9"/>
+      <c r="AC173" s="9"/>
+    </row>
+    <row r="174" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C174" s="9"/>
       <c r="D174" s="9"/>
       <c r="E174" s="9"/>
@@ -8002,8 +8128,11 @@
       <c r="X174" s="9"/>
       <c r="Y174" s="9"/>
       <c r="Z174" s="9"/>
-    </row>
-    <row r="175" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA174" s="9"/>
+      <c r="AB174" s="9"/>
+      <c r="AC174" s="9"/>
+    </row>
+    <row r="175" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C175" s="9"/>
       <c r="D175" s="9"/>
       <c r="E175" s="9"/>
@@ -8028,8 +8157,11 @@
       <c r="X175" s="9"/>
       <c r="Y175" s="9"/>
       <c r="Z175" s="9"/>
-    </row>
-    <row r="176" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA175" s="9"/>
+      <c r="AB175" s="9"/>
+      <c r="AC175" s="9"/>
+    </row>
+    <row r="176" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C176" s="9"/>
       <c r="D176" s="9"/>
       <c r="E176" s="9"/>
@@ -8054,8 +8186,11 @@
       <c r="X176" s="9"/>
       <c r="Y176" s="9"/>
       <c r="Z176" s="9"/>
-    </row>
-    <row r="177" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA176" s="9"/>
+      <c r="AB176" s="9"/>
+      <c r="AC176" s="9"/>
+    </row>
+    <row r="177" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C177" s="9"/>
       <c r="D177" s="9"/>
       <c r="E177" s="9"/>
@@ -8080,8 +8215,11 @@
       <c r="X177" s="9"/>
       <c r="Y177" s="9"/>
       <c r="Z177" s="9"/>
-    </row>
-    <row r="178" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA177" s="9"/>
+      <c r="AB177" s="9"/>
+      <c r="AC177" s="9"/>
+    </row>
+    <row r="178" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C178" s="9"/>
       <c r="D178" s="9"/>
       <c r="E178" s="9"/>
@@ -8106,8 +8244,11 @@
       <c r="X178" s="9"/>
       <c r="Y178" s="9"/>
       <c r="Z178" s="9"/>
-    </row>
-    <row r="179" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA178" s="9"/>
+      <c r="AB178" s="9"/>
+      <c r="AC178" s="9"/>
+    </row>
+    <row r="179" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C179" s="9"/>
       <c r="D179" s="9"/>
       <c r="E179" s="9"/>
@@ -8132,8 +8273,11 @@
       <c r="X179" s="9"/>
       <c r="Y179" s="9"/>
       <c r="Z179" s="9"/>
-    </row>
-    <row r="180" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA179" s="9"/>
+      <c r="AB179" s="9"/>
+      <c r="AC179" s="9"/>
+    </row>
+    <row r="180" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C180" s="9"/>
       <c r="D180" s="9"/>
       <c r="E180" s="9"/>
@@ -8158,8 +8302,11 @@
       <c r="X180" s="9"/>
       <c r="Y180" s="9"/>
       <c r="Z180" s="9"/>
-    </row>
-    <row r="181" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA180" s="9"/>
+      <c r="AB180" s="9"/>
+      <c r="AC180" s="9"/>
+    </row>
+    <row r="181" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C181" s="9"/>
       <c r="D181" s="9"/>
       <c r="E181" s="9"/>
@@ -8184,8 +8331,11 @@
       <c r="X181" s="9"/>
       <c r="Y181" s="9"/>
       <c r="Z181" s="9"/>
-    </row>
-    <row r="182" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA181" s="9"/>
+      <c r="AB181" s="9"/>
+      <c r="AC181" s="9"/>
+    </row>
+    <row r="182" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C182" s="9"/>
       <c r="D182" s="9"/>
       <c r="E182" s="9"/>
@@ -8210,8 +8360,11 @@
       <c r="X182" s="9"/>
       <c r="Y182" s="9"/>
       <c r="Z182" s="9"/>
-    </row>
-    <row r="183" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA182" s="9"/>
+      <c r="AB182" s="9"/>
+      <c r="AC182" s="9"/>
+    </row>
+    <row r="183" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C183" s="9"/>
       <c r="D183" s="9"/>
       <c r="E183" s="9"/>
@@ -8236,8 +8389,11 @@
       <c r="X183" s="9"/>
       <c r="Y183" s="9"/>
       <c r="Z183" s="9"/>
-    </row>
-    <row r="184" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA183" s="9"/>
+      <c r="AB183" s="9"/>
+      <c r="AC183" s="9"/>
+    </row>
+    <row r="184" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C184" s="9"/>
       <c r="D184" s="9"/>
       <c r="E184" s="9"/>
@@ -8262,8 +8418,11 @@
       <c r="X184" s="9"/>
       <c r="Y184" s="9"/>
       <c r="Z184" s="9"/>
-    </row>
-    <row r="185" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA184" s="9"/>
+      <c r="AB184" s="9"/>
+      <c r="AC184" s="9"/>
+    </row>
+    <row r="185" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C185" s="9"/>
       <c r="D185" s="9"/>
       <c r="E185" s="9"/>
@@ -8288,8 +8447,11 @@
       <c r="X185" s="9"/>
       <c r="Y185" s="9"/>
       <c r="Z185" s="9"/>
-    </row>
-    <row r="186" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA185" s="9"/>
+      <c r="AB185" s="9"/>
+      <c r="AC185" s="9"/>
+    </row>
+    <row r="186" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C186" s="9"/>
       <c r="D186" s="9"/>
       <c r="E186" s="9"/>
@@ -8314,8 +8476,11 @@
       <c r="X186" s="9"/>
       <c r="Y186" s="9"/>
       <c r="Z186" s="9"/>
-    </row>
-    <row r="187" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA186" s="9"/>
+      <c r="AB186" s="9"/>
+      <c r="AC186" s="9"/>
+    </row>
+    <row r="187" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C187" s="9"/>
       <c r="D187" s="9"/>
       <c r="E187" s="9"/>
@@ -8340,8 +8505,11 @@
       <c r="X187" s="9"/>
       <c r="Y187" s="9"/>
       <c r="Z187" s="9"/>
-    </row>
-    <row r="188" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA187" s="9"/>
+      <c r="AB187" s="9"/>
+      <c r="AC187" s="9"/>
+    </row>
+    <row r="188" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C188" s="9"/>
       <c r="D188" s="9"/>
       <c r="E188" s="9"/>
@@ -8366,8 +8534,11 @@
       <c r="X188" s="9"/>
       <c r="Y188" s="9"/>
       <c r="Z188" s="9"/>
-    </row>
-    <row r="189" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA188" s="9"/>
+      <c r="AB188" s="9"/>
+      <c r="AC188" s="9"/>
+    </row>
+    <row r="189" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C189" s="9"/>
       <c r="D189" s="9"/>
       <c r="E189" s="9"/>
@@ -8392,8 +8563,11 @@
       <c r="X189" s="9"/>
       <c r="Y189" s="9"/>
       <c r="Z189" s="9"/>
-    </row>
-    <row r="190" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA189" s="9"/>
+      <c r="AB189" s="9"/>
+      <c r="AC189" s="9"/>
+    </row>
+    <row r="190" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C190" s="9"/>
       <c r="D190" s="9"/>
       <c r="E190" s="9"/>
@@ -8418,8 +8592,11 @@
       <c r="X190" s="9"/>
       <c r="Y190" s="9"/>
       <c r="Z190" s="9"/>
-    </row>
-    <row r="191" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA190" s="9"/>
+      <c r="AB190" s="9"/>
+      <c r="AC190" s="9"/>
+    </row>
+    <row r="191" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C191" s="9"/>
       <c r="D191" s="9"/>
       <c r="E191" s="9"/>
@@ -8444,8 +8621,11 @@
       <c r="X191" s="9"/>
       <c r="Y191" s="9"/>
       <c r="Z191" s="9"/>
-    </row>
-    <row r="192" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA191" s="9"/>
+      <c r="AB191" s="9"/>
+      <c r="AC191" s="9"/>
+    </row>
+    <row r="192" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C192" s="9"/>
       <c r="D192" s="9"/>
       <c r="E192" s="9"/>
@@ -8470,8 +8650,11 @@
       <c r="X192" s="9"/>
       <c r="Y192" s="9"/>
       <c r="Z192" s="9"/>
-    </row>
-    <row r="193" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA192" s="9"/>
+      <c r="AB192" s="9"/>
+      <c r="AC192" s="9"/>
+    </row>
+    <row r="193" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C193" s="9"/>
       <c r="D193" s="9"/>
       <c r="E193" s="9"/>
@@ -8496,8 +8679,11 @@
       <c r="X193" s="9"/>
       <c r="Y193" s="9"/>
       <c r="Z193" s="9"/>
-    </row>
-    <row r="194" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA193" s="9"/>
+      <c r="AB193" s="9"/>
+      <c r="AC193" s="9"/>
+    </row>
+    <row r="194" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C194" s="9"/>
       <c r="D194" s="9"/>
       <c r="E194" s="9"/>
@@ -8522,8 +8708,11 @@
       <c r="X194" s="9"/>
       <c r="Y194" s="9"/>
       <c r="Z194" s="9"/>
-    </row>
-    <row r="195" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA194" s="9"/>
+      <c r="AB194" s="9"/>
+      <c r="AC194" s="9"/>
+    </row>
+    <row r="195" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C195" s="9"/>
       <c r="D195" s="9"/>
       <c r="E195" s="9"/>
@@ -8548,8 +8737,11 @@
       <c r="X195" s="9"/>
       <c r="Y195" s="9"/>
       <c r="Z195" s="9"/>
-    </row>
-    <row r="196" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA195" s="9"/>
+      <c r="AB195" s="9"/>
+      <c r="AC195" s="9"/>
+    </row>
+    <row r="196" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C196" s="9"/>
       <c r="D196" s="9"/>
       <c r="E196" s="9"/>
@@ -8574,8 +8766,11 @@
       <c r="X196" s="9"/>
       <c r="Y196" s="9"/>
       <c r="Z196" s="9"/>
-    </row>
-    <row r="197" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA196" s="9"/>
+      <c r="AB196" s="9"/>
+      <c r="AC196" s="9"/>
+    </row>
+    <row r="197" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C197" s="9"/>
       <c r="D197" s="9"/>
       <c r="E197" s="9"/>
@@ -8600,8 +8795,11 @@
       <c r="X197" s="9"/>
       <c r="Y197" s="9"/>
       <c r="Z197" s="9"/>
-    </row>
-    <row r="198" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA197" s="9"/>
+      <c r="AB197" s="9"/>
+      <c r="AC197" s="9"/>
+    </row>
+    <row r="198" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C198" s="9"/>
       <c r="D198" s="9"/>
       <c r="E198" s="9"/>
@@ -8626,8 +8824,11 @@
       <c r="X198" s="9"/>
       <c r="Y198" s="9"/>
       <c r="Z198" s="9"/>
-    </row>
-    <row r="199" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA198" s="9"/>
+      <c r="AB198" s="9"/>
+      <c r="AC198" s="9"/>
+    </row>
+    <row r="199" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C199" s="9"/>
       <c r="D199" s="9"/>
       <c r="E199" s="9"/>
@@ -8652,8 +8853,11 @@
       <c r="X199" s="9"/>
       <c r="Y199" s="9"/>
       <c r="Z199" s="9"/>
-    </row>
-    <row r="200" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA199" s="9"/>
+      <c r="AB199" s="9"/>
+      <c r="AC199" s="9"/>
+    </row>
+    <row r="200" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C200" s="9"/>
       <c r="D200" s="9"/>
       <c r="E200" s="9"/>
@@ -8678,23 +8882,874 @@
       <c r="X200" s="9"/>
       <c r="Y200" s="9"/>
       <c r="Z200" s="9"/>
+      <c r="AA200" s="9"/>
+      <c r="AB200" s="9"/>
+      <c r="AC200" s="9"/>
     </row>
   </sheetData>
+  <autoFilter ref="A2:AC200" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <mergeCells count="2">
     <mergeCell ref="C1:O1"/>
-    <mergeCell ref="P1:Z1"/>
+    <mergeCell ref="P1:AC1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3:Z200">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>AND($B3&lt;&gt;"",C3="")</formula>
+  <conditionalFormatting sqref="C3:AZ200">
+    <cfRule type="expression" dxfId="3" priority="7" stopIfTrue="1">
+      <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>AND(C3&lt;&gt;"",ISNUMBER(C3))</formula>
+    <cfRule type="expression" dxfId="5" priority="8" stopIfTrue="1">
+      <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&gt;30,(EDATE(C3,12)-TODAY())&lt;=60)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="9" stopIfTrue="1">
+      <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&gt;60)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="15"/>
+      <c r="G3" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="15"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="14">
+        <f>COUNTA(Contractors!A2:A50)</f>
+        <v>2</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="14">
+        <f>COUNTA(Workers!A2:A200)</f>
+        <v>16</v>
+      </c>
+      <c r="D4" s="15"/>
+      <c r="E4" s="14">
+        <f>COUNTIFS(Workers!A2:A200,"&lt;&gt;",Workers!D2:D200,"active")</f>
+        <v>16</v>
+      </c>
+      <c r="F4" s="15"/>
+      <c r="G4" s="14" t="str">
+        <f ca="1">TEXT(TODAY(),"mm/dd/yyyy")</f>
+        <v>04/24/2026</v>
+      </c>
+      <c r="H4" s="15"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+    </row>
+    <row r="7" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="str">
+        <f>Certifications!A2</f>
+        <v>Protección Contra Caídas</v>
+      </c>
+      <c r="B9" s="2" t="str">
+        <f>Certifications!B2</f>
+        <v>HSE Required</v>
+      </c>
+      <c r="C9" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A9,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>14</v>
+      </c>
+      <c r="D9" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C9</f>
+        <v>2</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" ref="E9:E35" si="0">IFERROR(C9/(C9+D9),0)</f>
+        <v>0.875</v>
+      </c>
+      <c r="F9" s="4" t="str">
+        <f t="shared" ref="F9:F35" si="1">REPT("■",ROUND(E9*20,0))</f>
+        <v>■■■■■■■■■■■■■■■■■■</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="str">
+        <f>Certifications!A3</f>
+        <v>Flama Expuesta</v>
+      </c>
+      <c r="B10" s="2" t="str">
+        <f>Certifications!B3</f>
+        <v>HSE Required</v>
+      </c>
+      <c r="C10" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A10,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C10</f>
+        <v>16</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="str">
+        <f>Certifications!A4</f>
+        <v>Espacios Confinados</v>
+      </c>
+      <c r="B11" s="2" t="str">
+        <f>Certifications!B4</f>
+        <v>HSE Required</v>
+      </c>
+      <c r="C11" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A11,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>8</v>
+      </c>
+      <c r="D11" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C11</f>
+        <v>8</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■■■■■■■</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="str">
+        <f>Certifications!A5</f>
+        <v>Manejo de Equipo Motorizado</v>
+      </c>
+      <c r="B12" s="2" t="str">
+        <f>Certifications!B5</f>
+        <v>HSE Required</v>
+      </c>
+      <c r="C12" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A12,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>4</v>
+      </c>
+      <c r="D12" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C12</f>
+        <v>12</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="F12" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■■</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="str">
+        <f>Certifications!A6</f>
+        <v>Excavación o Zanja</v>
+      </c>
+      <c r="B13" s="2" t="str">
+        <f>Certifications!B6</f>
+        <v>HSE Required</v>
+      </c>
+      <c r="C13" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A13,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>8</v>
+      </c>
+      <c r="D13" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C13</f>
+        <v>8</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■■■■■■■</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="str">
+        <f>Certifications!A7</f>
+        <v>Manejo de Tijeras (Scissor Lift)</v>
+      </c>
+      <c r="B14" s="2" t="str">
+        <f>Certifications!B7</f>
+        <v>HSE Required</v>
+      </c>
+      <c r="C14" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A14,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>9</v>
+      </c>
+      <c r="D14" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C14</f>
+        <v>7</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>0.5625</v>
+      </c>
+      <c r="F14" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■■■■■■■■</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="str">
+        <f>Certifications!A8</f>
+        <v>Seguridad Eléctrica</v>
+      </c>
+      <c r="B15" s="2" t="str">
+        <f>Certifications!B8</f>
+        <v>HSE Required</v>
+      </c>
+      <c r="C15" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A15,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>9</v>
+      </c>
+      <c r="D15" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C15</f>
+        <v>7</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="0"/>
+        <v>0.5625</v>
+      </c>
+      <c r="F15" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■■■■■■■■</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="str">
+        <f>Certifications!A9</f>
+        <v>Lockout</v>
+      </c>
+      <c r="B16" s="2" t="str">
+        <f>Certifications!B9</f>
+        <v>HSE Required</v>
+      </c>
+      <c r="C16" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A16,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>9</v>
+      </c>
+      <c r="D16" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C16</f>
+        <v>7</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="0"/>
+        <v>0.5625</v>
+      </c>
+      <c r="F16" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■■■■■■■■</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="str">
+        <f>Certifications!A10</f>
+        <v>Manejo de Grúas</v>
+      </c>
+      <c r="B17" s="2" t="str">
+        <f>Certifications!B10</f>
+        <v>HSE Required</v>
+      </c>
+      <c r="C17" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A17,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>4</v>
+      </c>
+      <c r="D17" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C17</f>
+        <v>12</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="F17" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■■</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="str">
+        <f>Certifications!A11</f>
+        <v>Escaleras</v>
+      </c>
+      <c r="B18" s="2" t="str">
+        <f>Certifications!B11</f>
+        <v>HSE Required</v>
+      </c>
+      <c r="C18" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A18,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>8</v>
+      </c>
+      <c r="D18" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C18</f>
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="F18" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■■■■■■■</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="str">
+        <f>Certifications!A12</f>
+        <v>Andamios</v>
+      </c>
+      <c r="B19" s="2" t="str">
+        <f>Certifications!B12</f>
+        <v>HSE Required</v>
+      </c>
+      <c r="C19" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A19,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>3</v>
+      </c>
+      <c r="D19" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C19</f>
+        <v>13</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="0"/>
+        <v>0.1875</v>
+      </c>
+      <c r="F19" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="str">
+        <f>Certifications!A13</f>
+        <v>Trabajos con Plomo o Asbesto</v>
+      </c>
+      <c r="B20" s="2" t="str">
+        <f>Certifications!B13</f>
+        <v>HSE Required</v>
+      </c>
+      <c r="C20" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A20,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C20</f>
+        <v>16</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="str">
+        <f>Certifications!A14</f>
+        <v>Comunicación de Riesgos</v>
+      </c>
+      <c r="B21" s="2" t="str">
+        <f>Certifications!B14</f>
+        <v>HSE Required</v>
+      </c>
+      <c r="C21" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A21,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>14</v>
+      </c>
+      <c r="D21" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C21</f>
+        <v>2</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="0"/>
+        <v>0.875</v>
+      </c>
+      <c r="F21" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■■■■■■■■■■■■■■■</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="str">
+        <f>Certifications!A15</f>
+        <v>Inducción Jacobs/Lilly</v>
+      </c>
+      <c r="B22" s="2" t="str">
+        <f>Certifications!B15</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C22" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A22,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>7</v>
+      </c>
+      <c r="D22" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C22</f>
+        <v>9</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="0"/>
+        <v>0.4375</v>
+      </c>
+      <c r="F22" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■■■■■■</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="str">
+        <f>Certifications!A16</f>
+        <v>OSHA 40Hr HAZWOPER</v>
+      </c>
+      <c r="B23" s="2" t="str">
+        <f>Certifications!B16</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C23" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A23,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>6</v>
+      </c>
+      <c r="D23" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C23</f>
+        <v>10</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+      <c r="F23" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■■■■■</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="str">
+        <f>Certifications!A17</f>
+        <v>OSHA 8Hr Refresher</v>
+      </c>
+      <c r="B24" s="2" t="str">
+        <f>Certifications!B17</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C24" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A24,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>6</v>
+      </c>
+      <c r="D24" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C24</f>
+        <v>10</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+      <c r="F24" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■■■■■</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="str">
+        <f>Certifications!A18</f>
+        <v>Drilling Safety</v>
+      </c>
+      <c r="B25" s="2" t="str">
+        <f>Certifications!B18</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C25" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A25,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>6</v>
+      </c>
+      <c r="D25" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C25</f>
+        <v>10</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+      <c r="F25" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■■■■■</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="str">
+        <f>Certifications!A19</f>
+        <v>Utility Locating</v>
+      </c>
+      <c r="B26" s="2" t="str">
+        <f>Certifications!B19</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C26" s="2">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A26,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>2</v>
+      </c>
+      <c r="D26" s="2">
+        <f>COUNTA(Workers!A$2:A$200)-C26</f>
+        <v>14</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+      <c r="F26" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="str">
+        <f>Certifications!A20</f>
+        <v>OSHA 10</v>
+      </c>
+      <c r="B27" s="11" t="str">
+        <f>Certifications!B20</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C27" s="11">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A27,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>6</v>
+      </c>
+      <c r="D27" s="11">
+        <f>COUNTA(Workers!A$2:A$200)-C27</f>
+        <v>10</v>
+      </c>
+      <c r="E27" s="12">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+      <c r="F27" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■■■■■</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="str">
+        <f>Certifications!A21</f>
+        <v>OSHA 30</v>
+      </c>
+      <c r="B28" s="11" t="str">
+        <f>Certifications!B21</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C28" s="11">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A28,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>3</v>
+      </c>
+      <c r="D28" s="11">
+        <f>COUNTA(Workers!A$2:A$200)-C28</f>
+        <v>13</v>
+      </c>
+      <c r="E28" s="12">
+        <f t="shared" si="0"/>
+        <v>0.1875</v>
+      </c>
+      <c r="F28" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="str">
+        <f>Certifications!A22</f>
+        <v>Rebar Safety</v>
+      </c>
+      <c r="B29" s="11" t="str">
+        <f>Certifications!B22</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C29" s="11">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A29,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>3</v>
+      </c>
+      <c r="D29" s="11">
+        <f>COUNTA(Workers!A$2:A$200)-C29</f>
+        <v>13</v>
+      </c>
+      <c r="E29" s="12">
+        <f t="shared" si="0"/>
+        <v>0.1875</v>
+      </c>
+      <c r="F29" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="str">
+        <f>Certifications!A23</f>
+        <v>Formwork &amp; Shoring</v>
+      </c>
+      <c r="B30" s="11" t="str">
+        <f>Certifications!B23</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C30" s="11">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A30,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>3</v>
+      </c>
+      <c r="D30" s="11">
+        <f>COUNTA(Workers!A$2:A$200)-C30</f>
+        <v>13</v>
+      </c>
+      <c r="E30" s="12">
+        <f t="shared" si="0"/>
+        <v>0.1875</v>
+      </c>
+      <c r="F30" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="str">
+        <f>Certifications!A24</f>
+        <v>Silica Exposure</v>
+      </c>
+      <c r="B31" s="11" t="str">
+        <f>Certifications!B24</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C31" s="11">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A31,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>3</v>
+      </c>
+      <c r="D31" s="11">
+        <f>COUNTA(Workers!A$2:A$200)-C31</f>
+        <v>13</v>
+      </c>
+      <c r="E31" s="12">
+        <f t="shared" si="0"/>
+        <v>0.1875</v>
+      </c>
+      <c r="F31" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="str">
+        <f>Certifications!A25</f>
+        <v>Concrete &amp; Masonry</v>
+      </c>
+      <c r="B32" s="11" t="str">
+        <f>Certifications!B25</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C32" s="11">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A32,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>3</v>
+      </c>
+      <c r="D32" s="11">
+        <f>COUNTA(Workers!A$2:A$200)-C32</f>
+        <v>13</v>
+      </c>
+      <c r="E32" s="12">
+        <f t="shared" si="0"/>
+        <v>0.1875</v>
+      </c>
+      <c r="F32" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>■■■■</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="str">
+        <f>Certifications!A26</f>
+        <v>Equipment Training</v>
+      </c>
+      <c r="B33" s="11" t="str">
+        <f>Certifications!B26</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C33" s="11">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A33,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>1</v>
+      </c>
+      <c r="D33" s="11">
+        <f>COUNTA(Workers!A$2:A$200)-C33</f>
+        <v>15</v>
+      </c>
+      <c r="E33" s="12">
+        <f t="shared" si="0"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="F33" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>■</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="str">
+        <f>Certifications!A27</f>
+        <v>OSHA 30 501</v>
+      </c>
+      <c r="B34" s="11" t="str">
+        <f>Certifications!B27</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C34" s="11">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A34,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>1</v>
+      </c>
+      <c r="D34" s="11">
+        <f>COUNTA(Workers!A$2:A$200)-C34</f>
+        <v>15</v>
+      </c>
+      <c r="E34" s="12">
+        <f t="shared" si="0"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="F34" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>■</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="str">
+        <f>Certifications!A28</f>
+        <v>OSHA 30 511</v>
+      </c>
+      <c r="B35" s="11" t="str">
+        <f>Certifications!B28</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C35" s="11">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A35,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>1</v>
+      </c>
+      <c r="D35" s="11">
+        <f>COUNTA(Workers!A$2:A$200)-C35</f>
+        <v>15</v>
+      </c>
+      <c r="E35" s="12">
+        <f t="shared" si="0"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="F35" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>■</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="G4:H5"/>
+    <mergeCell ref="E4:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E9:E26">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="lessThan">
+      <formula>0.7</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="between">
+      <formula>0.7</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cert_tracker/Contractor Certifications Tracker.xlsx
+++ b/cert_tracker/Contractor Certifications Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsant\jacobdashboard\cert_tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851FFCEC-3A94-489A-A63E-B0D2EFC83723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7A1FC5-C730-41EA-93BF-A26A0FBA3A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="607" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Dashboard" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Tracker!$A$2:$AC$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Tracker!$A$2:$AD$200</definedName>
     <definedName name="ContractorOption" comment="=Workers!$B$2:INDEX(Workers!$B:$B,LOOKUP(2,1/(Workers!$B:$B&lt;&gt;&quot;&quot;),ROW(Workers!$B:$B)))">Workers!$B$2:INDEX(Workers!$B:$B,LOOKUP(2,1/(Workers!$B:$B&lt;&gt;""),ROW(Workers!$B:$B)))</definedName>
     <definedName name="JobTitleOptions">Workers!$C$2:INDEX(Workers!$C:$C,LOOKUP(2,1/(Workers!$C:$C&lt;&gt;""),ROW(Workers!$C:$C)))</definedName>
   </definedNames>
@@ -43,7 +43,271 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="98">
+  <si>
+    <t>HSE Required Certifications</t>
+  </si>
+  <si>
+    <t>Additional Training</t>
+  </si>
+  <si>
+    <t>Contractor</t>
+  </si>
+  <si>
+    <t>Worker</t>
+  </si>
+  <si>
+    <t>GeoEnviroTech, Inc.</t>
+  </si>
+  <si>
+    <t>William Rodriguez Rivera</t>
+  </si>
+  <si>
+    <t>Hardy Rodríguez Vázquez</t>
+  </si>
+  <si>
+    <t>Juan D. Negrón Hernández</t>
+  </si>
+  <si>
+    <t>Rafael Díaz Colón</t>
+  </si>
+  <si>
+    <t>Luis A. Padilla Díaz</t>
+  </si>
+  <si>
+    <t>Jesús Quiñonez Ayala</t>
+  </si>
+  <si>
+    <t>Cornerstone Industrial Group, Corp</t>
+  </si>
+  <si>
+    <t>Héctor M. Rodríguez Alicea</t>
+  </si>
+  <si>
+    <t>Rene J. Torres Blasini</t>
+  </si>
+  <si>
+    <t>Jorge L. Figueroa Torres</t>
+  </si>
+  <si>
+    <t>Giovani Torres</t>
+  </si>
+  <si>
+    <t>Santos Rivera Tirado</t>
+  </si>
+  <si>
+    <t>José J. Rincon</t>
+  </si>
+  <si>
+    <t>Carlos O. Luhring</t>
+  </si>
+  <si>
+    <t>Felipe Lopez Dinardi</t>
+  </si>
+  <si>
+    <t>Francisco González Carmona</t>
+  </si>
+  <si>
+    <t>Steven Cruz Martínez</t>
+  </si>
+  <si>
+    <t>Contractor Certifications Tracker</t>
+  </si>
+  <si>
+    <t>How to use this workbook</t>
+  </si>
+  <si>
+    <t>1. Add new contractors on the Contractors tab.</t>
+  </si>
+  <si>
+    <t>2. Add workers on the Workers tab. Each worker belongs to one contractor (pick from dropdown).</t>
+  </si>
+  <si>
+    <t>3. Review required certifications on the Certifications tab. Add new ones if HSE adds them.</t>
+  </si>
+  <si>
+    <t>4. On the Tracker tab, enter the completion date for each worker / certification combo.</t>
+  </si>
+  <si>
+    <t>5. The Dashboard tab auto-updates: compliance %, missing certs, expiring soon.</t>
+  </si>
+  <si>
+    <t>Color coding on the Tracker</t>
+  </si>
+  <si>
+    <t>• Red cell     = certification missing (empty)</t>
+  </si>
+  <si>
+    <t>• Yellow cell  = completed, expiring within 60 days</t>
+  </si>
+  <si>
+    <t>• Orange cell  = expired (past validity based on Certifications tab)</t>
+  </si>
+  <si>
+    <t>• Green cell   = current</t>
+  </si>
+  <si>
+    <t>Sharing with peers</t>
+  </si>
+  <si>
+    <t>Save this file to OneDrive or SharePoint and turn on co-authoring so peers can edit simultaneously.</t>
+  </si>
+  <si>
+    <t>Every edit is tracked in Version History (File → Info → Version History).</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>• Validity years in the Certifications tab drive expiration logic. 0 = no expiration.</t>
+  </si>
+  <si>
+    <t>• Dates must be entered as real dates (mm/dd/yyyy), not text.</t>
+  </si>
+  <si>
+    <t>Certification</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Validity (years, 0=none)</t>
+  </si>
+  <si>
+    <t>Protección Contra Caídas</t>
+  </si>
+  <si>
+    <t>HSE Required</t>
+  </si>
+  <si>
+    <t>Flama Expuesta</t>
+  </si>
+  <si>
+    <t>Espacios Confinados</t>
+  </si>
+  <si>
+    <t>Manejo de Equipo Motorizado</t>
+  </si>
+  <si>
+    <t>Excavación o Zanja</t>
+  </si>
+  <si>
+    <t>Manejo de Tijeras (Scissor Lift)</t>
+  </si>
+  <si>
+    <t>Seguridad Eléctrica</t>
+  </si>
+  <si>
+    <t>Lockout</t>
+  </si>
+  <si>
+    <t>Manejo de Grúas</t>
+  </si>
+  <si>
+    <t>Escaleras</t>
+  </si>
+  <si>
+    <t>Andamios</t>
+  </si>
+  <si>
+    <t>Trabajos con Plomo o Asbesto</t>
+  </si>
+  <si>
+    <t>Comunicación de Riesgos</t>
+  </si>
+  <si>
+    <t>Inducción Jacobs/Lilly</t>
+  </si>
+  <si>
+    <t>OSHA 40Hr HAZWOPER</t>
+  </si>
+  <si>
+    <t>OSHA 8Hr Refresher</t>
+  </si>
+  <si>
+    <t>Drilling Safety</t>
+  </si>
+  <si>
+    <t>Utility Locating</t>
+  </si>
+  <si>
+    <t>OSHA 10</t>
+  </si>
+  <si>
+    <t>OSHA 30</t>
+  </si>
+  <si>
+    <t>Rebar Safety</t>
+  </si>
+  <si>
+    <t>Formwork &amp; Shoring</t>
+  </si>
+  <si>
+    <t>Silica Exposure</t>
+  </si>
+  <si>
+    <t>Concrete &amp; Masonry</t>
+  </si>
+  <si>
+    <t>Equipment Training</t>
+  </si>
+  <si>
+    <t>OSHA 30 501</t>
+  </si>
+  <si>
+    <t>OSHA 30 511</t>
+  </si>
+  <si>
+    <t>Contractor Name</t>
+  </si>
+  <si>
+    <t>Primary Contact</t>
+  </si>
+  <si>
+    <t>Specialty</t>
+  </si>
+  <si>
+    <t>Workers (count)</t>
+  </si>
+  <si>
+    <t>Juan D. Negrón, PG</t>
+  </si>
+  <si>
+    <t>Drilling / Geotechnical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Civil Construction                                                                    </t>
+  </si>
+  <si>
+    <t>Worker Name</t>
+  </si>
+  <si>
+    <t>Job Title</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Employee Code</t>
+  </si>
+  <si>
+    <t>Hire Date</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Project Geologist</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Civil Constructor</t>
+  </si>
   <si>
     <t>Contractor Certifications Dashboard</t>
   </si>
@@ -63,12 +327,6 @@
     <t>Compliance by Certification</t>
   </si>
   <si>
-    <t>Certification</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
     <t>Completed</t>
   </si>
   <si>
@@ -79,264 +337,6 @@
   </si>
   <si>
     <t>Bar</t>
-  </si>
-  <si>
-    <t>Contractor Certifications Tracker</t>
-  </si>
-  <si>
-    <t>How to use this workbook</t>
-  </si>
-  <si>
-    <t>1. Add new contractors on the Contractors tab.</t>
-  </si>
-  <si>
-    <t>2. Add workers on the Workers tab. Each worker belongs to one contractor (pick from dropdown).</t>
-  </si>
-  <si>
-    <t>3. Review required certifications on the Certifications tab. Add new ones if HSE adds them.</t>
-  </si>
-  <si>
-    <t>4. On the Tracker tab, enter the completion date for each worker / certification combo.</t>
-  </si>
-  <si>
-    <t>5. The Dashboard tab auto-updates: compliance %, missing certs, expiring soon.</t>
-  </si>
-  <si>
-    <t>Color coding on the Tracker</t>
-  </si>
-  <si>
-    <t>• Red cell     = certification missing (empty)</t>
-  </si>
-  <si>
-    <t>• Yellow cell  = completed, expiring within 60 days</t>
-  </si>
-  <si>
-    <t>• Orange cell  = expired (past validity based on Certifications tab)</t>
-  </si>
-  <si>
-    <t>• Green cell   = current</t>
-  </si>
-  <si>
-    <t>Sharing with peers</t>
-  </si>
-  <si>
-    <t>Save this file to OneDrive or SharePoint and turn on co-authoring so peers can edit simultaneously.</t>
-  </si>
-  <si>
-    <t>Every edit is tracked in Version History (File → Info → Version History).</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>• Validity years in the Certifications tab drive expiration logic. 0 = no expiration.</t>
-  </si>
-  <si>
-    <t>• Dates must be entered as real dates (mm/dd/yyyy), not text.</t>
-  </si>
-  <si>
-    <t>Validity (years, 0=none)</t>
-  </si>
-  <si>
-    <t>Protección Contra Caídas</t>
-  </si>
-  <si>
-    <t>HSE Required</t>
-  </si>
-  <si>
-    <t>Flama Expuesta</t>
-  </si>
-  <si>
-    <t>Espacios Confinados</t>
-  </si>
-  <si>
-    <t>Manejo de Equipo Motorizado</t>
-  </si>
-  <si>
-    <t>Excavación o Zanja</t>
-  </si>
-  <si>
-    <t>Manejo de Tijeras (Scissor Lift)</t>
-  </si>
-  <si>
-    <t>Seguridad Eléctrica</t>
-  </si>
-  <si>
-    <t>Lockout</t>
-  </si>
-  <si>
-    <t>Manejo de Grúas</t>
-  </si>
-  <si>
-    <t>Escaleras</t>
-  </si>
-  <si>
-    <t>Andamios</t>
-  </si>
-  <si>
-    <t>Trabajos con Plomo o Asbesto</t>
-  </si>
-  <si>
-    <t>Comunicación de Riesgos</t>
-  </si>
-  <si>
-    <t>Inducción Jacobs/Lilly</t>
-  </si>
-  <si>
-    <t>Additional Training</t>
-  </si>
-  <si>
-    <t>OSHA 40Hr HAZWOPER</t>
-  </si>
-  <si>
-    <t>OSHA 8Hr Refresher</t>
-  </si>
-  <si>
-    <t>Drilling Safety</t>
-  </si>
-  <si>
-    <t>Utility Locating</t>
-  </si>
-  <si>
-    <t>OSHA 10</t>
-  </si>
-  <si>
-    <t>OSHA 30</t>
-  </si>
-  <si>
-    <t>Rebar Safety</t>
-  </si>
-  <si>
-    <t>Formwork &amp; Shoring</t>
-  </si>
-  <si>
-    <t>Silica Exposure</t>
-  </si>
-  <si>
-    <t>Concrete &amp; Masonry</t>
-  </si>
-  <si>
-    <t>Equipment Training</t>
-  </si>
-  <si>
-    <t>OSHA 30 501</t>
-  </si>
-  <si>
-    <t>OSHA 30 511</t>
-  </si>
-  <si>
-    <t>Contractor Name</t>
-  </si>
-  <si>
-    <t>Primary Contact</t>
-  </si>
-  <si>
-    <t>Specialty</t>
-  </si>
-  <si>
-    <t>Workers (count)</t>
-  </si>
-  <si>
-    <t>GeoEnviroTech, Inc.</t>
-  </si>
-  <si>
-    <t>Juan D. Negrón, PG</t>
-  </si>
-  <si>
-    <t>Drilling / Geotechnical</t>
-  </si>
-  <si>
-    <t>Cornerstone Industrial Group, Corp</t>
-  </si>
-  <si>
-    <t>Felipe Lopez Dinardi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Civil Construction                                                                    </t>
-  </si>
-  <si>
-    <t>Worker Name</t>
-  </si>
-  <si>
-    <t>Contractor</t>
-  </si>
-  <si>
-    <t>Job Title</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Employee Code</t>
-  </si>
-  <si>
-    <t>Hire Date</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>William Rodriguez Rivera</t>
-  </si>
-  <si>
-    <t>Project Geologist</t>
-  </si>
-  <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>Hardy Rodríguez Vázquez</t>
-  </si>
-  <si>
-    <t>Juan D. Negrón Hernández</t>
-  </si>
-  <si>
-    <t>Rafael Díaz Colón</t>
-  </si>
-  <si>
-    <t>Luis A. Padilla Díaz</t>
-  </si>
-  <si>
-    <t>Jesús Quiñonez Ayala</t>
-  </si>
-  <si>
-    <t>Héctor M. Rodríguez Alicea</t>
-  </si>
-  <si>
-    <t>Civil Constructor</t>
-  </si>
-  <si>
-    <t>Rene J. Torres Blasini</t>
-  </si>
-  <si>
-    <t>Jorge L. Figueroa Torres</t>
-  </si>
-  <si>
-    <t>Giovani Torres</t>
-  </si>
-  <si>
-    <t>Santos Rivera Tirado</t>
-  </si>
-  <si>
-    <t>José J. Rincon</t>
-  </si>
-  <si>
-    <t>Carlos O. Luhring</t>
-  </si>
-  <si>
-    <t>Francisco González Carmona</t>
-  </si>
-  <si>
-    <t>Steven Cruz Martínez</t>
-  </si>
-  <si>
-    <t>HSE Required Certifications</t>
-  </si>
-  <si>
-    <t>Worker</t>
   </si>
 </sst>
 </file>
@@ -347,7 +347,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -408,6 +408,11 @@
       <color rgb="FF2E7D32"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2E7D32"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -432,7 +437,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -470,11 +475,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -497,86 +517,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -599,10 +559,36 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEA4A4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFEA4A4"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -634,7 +620,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Contractor Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Primary Contact"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Specialty"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Workers (count)" dataDxfId="12">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Workers (count)" dataDxfId="6">
       <calculatedColumnFormula>IF(A2="","",COUNTIF(Workers!B:B,A2))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Notes"/>
@@ -953,46 +939,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="A1" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1000,27 +986,27 @@
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1028,17 +1014,17 @@
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -1046,17 +1032,17 @@
     </row>
     <row r="20" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1080,24 +1066,24 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1105,10 +1091,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1116,10 +1102,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1127,10 +1113,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -1138,10 +1124,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1149,10 +1135,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -1160,10 +1146,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1171,10 +1157,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1182,10 +1168,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -1193,10 +1179,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -1204,10 +1190,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -1215,10 +1201,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1226,10 +1212,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
         <v>44</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1237,10 +1223,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1248,10 +1234,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1259,10 +1245,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1270,10 +1256,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -1281,10 +1267,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1292,10 +1278,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1303,10 +1289,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1314,10 +1300,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1325,10 +1311,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1336,10 +1322,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1347,10 +1333,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1358,10 +1344,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1369,10 +1355,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1380,10 +1366,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1404,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -1416,30 +1402,30 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D2">
         <f>IF(A2="","",COUNTIF(Workers!B:B,A2))</f>
@@ -1448,13 +1434,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D3">
         <f>IF(A3="","",COUNTIF(Workers!B:B,A3))</f>
@@ -1463,282 +1449,276 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D4" t="str">
-        <f>IF(A4="","",COUNTIF(Workers!B:B,A4))</f>
+        <f>IF(A5="","",COUNTIF(Workers!B:B,A5))</f>
         <v/>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D5" t="str">
-        <f>IF(A5="","",COUNTIF(Workers!B:B,A5))</f>
+        <f>IF(A6="","",COUNTIF(Workers!B:B,A6))</f>
         <v/>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D6" t="str">
-        <f>IF(A6="","",COUNTIF(Workers!B:B,A6))</f>
+        <f>IF(A7="","",COUNTIF(Workers!B:B,A7))</f>
         <v/>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D7" t="str">
-        <f>IF(A7="","",COUNTIF(Workers!B:B,A7))</f>
+        <f>IF(A8="","",COUNTIF(Workers!B:B,A8))</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D8" t="str">
-        <f>IF(A8="","",COUNTIF(Workers!B:B,A8))</f>
+        <f>IF(A9="","",COUNTIF(Workers!B:B,A9))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D9" t="str">
-        <f>IF(A9="","",COUNTIF(Workers!B:B,A9))</f>
+        <f>IF(A10="","",COUNTIF(Workers!B:B,A10))</f>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D10" t="str">
-        <f>IF(A10="","",COUNTIF(Workers!B:B,A10))</f>
+        <f>IF(A11="","",COUNTIF(Workers!B:B,A11))</f>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D11" t="str">
-        <f>IF(A11="","",COUNTIF(Workers!B:B,A11))</f>
+        <f>IF(A12="","",COUNTIF(Workers!B:B,A12))</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D12" t="str">
-        <f>IF(A12="","",COUNTIF(Workers!B:B,A12))</f>
+        <f>IF(A13="","",COUNTIF(Workers!B:B,A13))</f>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D13" t="str">
-        <f>IF(A13="","",COUNTIF(Workers!B:B,A13))</f>
+        <f>IF(A14="","",COUNTIF(Workers!B:B,A14))</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D14" t="str">
-        <f>IF(A14="","",COUNTIF(Workers!B:B,A14))</f>
+        <f>IF(A15="","",COUNTIF(Workers!B:B,A15))</f>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D15" t="str">
-        <f>IF(A15="","",COUNTIF(Workers!B:B,A15))</f>
+        <f>IF(A16="","",COUNTIF(Workers!B:B,A16))</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16" t="str">
-        <f>IF(A16="","",COUNTIF(Workers!B:B,A16))</f>
+        <f>IF(A17="","",COUNTIF(Workers!B:B,A17))</f>
         <v/>
       </c>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D17" t="str">
-        <f>IF(A17="","",COUNTIF(Workers!B:B,A17))</f>
+        <f>IF(A18="","",COUNTIF(Workers!B:B,A18))</f>
         <v/>
       </c>
     </row>
     <row r="18" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D18" t="str">
-        <f>IF(A18="","",COUNTIF(Workers!B:B,A18))</f>
+        <f>IF(A19="","",COUNTIF(Workers!B:B,A19))</f>
         <v/>
       </c>
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" t="str">
-        <f>IF(A19="","",COUNTIF(Workers!B:B,A19))</f>
+        <f>IF(A20="","",COUNTIF(Workers!B:B,A20))</f>
         <v/>
       </c>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D20" t="str">
-        <f>IF(A20="","",COUNTIF(Workers!B:B,A20))</f>
+        <f>IF(A21="","",COUNTIF(Workers!B:B,A21))</f>
         <v/>
       </c>
     </row>
     <row r="21" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D21" t="str">
-        <f>IF(A21="","",COUNTIF(Workers!B:B,A21))</f>
+        <f>IF(A22="","",COUNTIF(Workers!B:B,A22))</f>
         <v/>
       </c>
     </row>
     <row r="22" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D22" t="str">
-        <f>IF(A22="","",COUNTIF(Workers!B:B,A22))</f>
+        <f>IF(A23="","",COUNTIF(Workers!B:B,A23))</f>
         <v/>
       </c>
     </row>
     <row r="23" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D23" t="str">
-        <f>IF(A23="","",COUNTIF(Workers!B:B,A23))</f>
+        <f>IF(A24="","",COUNTIF(Workers!B:B,A24))</f>
         <v/>
       </c>
     </row>
     <row r="24" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D24" t="str">
-        <f>IF(A24="","",COUNTIF(Workers!B:B,A24))</f>
+        <f>IF(A25="","",COUNTIF(Workers!B:B,A25))</f>
         <v/>
       </c>
     </row>
     <row r="25" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D25" t="str">
-        <f>IF(A25="","",COUNTIF(Workers!B:B,A25))</f>
+        <f>IF(A26="","",COUNTIF(Workers!B:B,A26))</f>
         <v/>
       </c>
     </row>
     <row r="26" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D26" t="str">
-        <f>IF(A26="","",COUNTIF(Workers!B:B,A26))</f>
+        <f>IF(A27="","",COUNTIF(Workers!B:B,A27))</f>
         <v/>
       </c>
     </row>
     <row r="27" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D27" t="str">
-        <f>IF(A27="","",COUNTIF(Workers!B:B,A27))</f>
+        <f>IF(A28="","",COUNTIF(Workers!B:B,A28))</f>
         <v/>
       </c>
     </row>
     <row r="28" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D28" t="str">
-        <f>IF(A28="","",COUNTIF(Workers!B:B,A28))</f>
+        <f>IF(A29="","",COUNTIF(Workers!B:B,A29))</f>
         <v/>
       </c>
     </row>
     <row r="29" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D29" t="str">
-        <f>IF(A29="","",COUNTIF(Workers!B:B,A29))</f>
+        <f>IF(A30="","",COUNTIF(Workers!B:B,A30))</f>
         <v/>
       </c>
     </row>
     <row r="30" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D30" t="str">
-        <f>IF(A30="","",COUNTIF(Workers!B:B,A30))</f>
+        <f>IF(A31="","",COUNTIF(Workers!B:B,A31))</f>
         <v/>
       </c>
     </row>
     <row r="31" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D31" t="str">
-        <f>IF(A31="","",COUNTIF(Workers!B:B,A31))</f>
+        <f>IF(A32="","",COUNTIF(Workers!B:B,A32))</f>
         <v/>
       </c>
     </row>
     <row r="32" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D32" t="str">
-        <f>IF(A32="","",COUNTIF(Workers!B:B,A32))</f>
+        <f>IF(A33="","",COUNTIF(Workers!B:B,A33))</f>
         <v/>
       </c>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D33" t="str">
-        <f>IF(A33="","",COUNTIF(Workers!B:B,A33))</f>
+        <f>IF(A34="","",COUNTIF(Workers!B:B,A34))</f>
         <v/>
       </c>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D34" t="str">
-        <f>IF(A34="","",COUNTIF(Workers!B:B,A34))</f>
+        <f>IF(A35="","",COUNTIF(Workers!B:B,A35))</f>
         <v/>
       </c>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D35" t="str">
-        <f>IF(A35="","",COUNTIF(Workers!B:B,A35))</f>
+        <f>IF(A36="","",COUNTIF(Workers!B:B,A36))</f>
         <v/>
       </c>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D36" t="str">
-        <f>IF(A36="","",COUNTIF(Workers!B:B,A36))</f>
+        <f>IF(A37="","",COUNTIF(Workers!B:B,A37))</f>
         <v/>
       </c>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D37" t="str">
-        <f>IF(A37="","",COUNTIF(Workers!B:B,A37))</f>
+        <f>IF(A38="","",COUNTIF(Workers!B:B,A38))</f>
         <v/>
       </c>
     </row>
     <row r="38" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D38" t="str">
-        <f>IF(A38="","",COUNTIF(Workers!B:B,A38))</f>
+        <f>IF(A39="","",COUNTIF(Workers!B:B,A39))</f>
         <v/>
       </c>
     </row>
     <row r="39" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D39" t="str">
-        <f>IF(A39="","",COUNTIF(Workers!B:B,A39))</f>
+        <f>IF(A40="","",COUNTIF(Workers!B:B,A40))</f>
         <v/>
       </c>
     </row>
     <row r="40" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D40" t="str">
-        <f>IF(A40="","",COUNTIF(Workers!B:B,A40))</f>
+        <f>IF(A41="","",COUNTIF(Workers!B:B,A41))</f>
         <v/>
       </c>
     </row>
     <row r="41" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D41" t="str">
-        <f>IF(A41="","",COUNTIF(Workers!B:B,A41))</f>
+        <f>IF(A42="","",COUNTIF(Workers!B:B,A42))</f>
         <v/>
       </c>
     </row>
     <row r="42" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D42" t="str">
-        <f>IF(A42="","",COUNTIF(Workers!B:B,A42))</f>
+        <f>IF(A43="","",COUNTIF(Workers!B:B,A43))</f>
         <v/>
       </c>
     </row>
     <row r="43" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D43" t="str">
-        <f>IF(A43="","",COUNTIF(Workers!B:B,A43))</f>
+        <f>IF(A44="","",COUNTIF(Workers!B:B,A44))</f>
         <v/>
       </c>
     </row>
     <row r="44" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D44" t="str">
-        <f>IF(A44="","",COUNTIF(Workers!B:B,A44))</f>
+        <f>IF(A45="","",COUNTIF(Workers!B:B,A45))</f>
         <v/>
       </c>
     </row>
     <row r="45" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D45" t="str">
-        <f>IF(A45="","",COUNTIF(Workers!B:B,A45))</f>
+        <f>IF(A46="","",COUNTIF(Workers!B:B,A46))</f>
         <v/>
       </c>
     </row>
     <row r="46" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D46" t="str">
-        <f>IF(A46="","",COUNTIF(Workers!B:B,A46))</f>
+        <f>IF(A47="","",COUNTIF(Workers!B:B,A47))</f>
         <v/>
       </c>
     </row>
     <row r="47" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D47" t="str">
-        <f>IF(A47="","",COUNTIF(Workers!B:B,A47))</f>
+        <f>IF(A48="","",COUNTIF(Workers!B:B,A48))</f>
         <v/>
       </c>
     </row>
     <row r="48" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D48" t="str">
-        <f>IF(A48="","",COUNTIF(Workers!B:B,A48))</f>
+        <f>IF(A49="","",COUNTIF(Workers!B:B,A49))</f>
         <v/>
       </c>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D49" t="str">
-        <f>IF(A49="","",COUNTIF(Workers!B:B,A49))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D50" t="str">
         <f>IF(A50="","",COUNTIF(Workers!B:B,A50))</f>
         <v/>
       </c>
@@ -1769,270 +1749,270 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
         <v>85</v>
       </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
         <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
         <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
         <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
         <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
         <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
         <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
         <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
         <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
         <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F16" s="7"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F17" s="7"/>
     </row>
@@ -2607,56 +2587,57 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AC200"/>
+  <dimension ref="A1:AD194"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="19" width="14" customWidth="1"/>
-    <col min="20" max="29" width="13" customWidth="1"/>
+    <col min="20" max="30" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
-      <c r="C1" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
-    </row>
-    <row r="2" spans="1:29" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="18"/>
+      <c r="AA1" s="18"/>
+      <c r="AB1" s="18"/>
+      <c r="AC1" s="18"/>
+      <c r="AD1" s="18"/>
+    </row>
+    <row r="2" spans="1:30" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="str">
         <f>Certifications!A2</f>
@@ -2767,12 +2748,12 @@
         <v>OSHA 30 511</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="C3" s="9">
         <v>45764</v>
@@ -2816,12 +2797,12 @@
       <c r="AB3" s="9"/>
       <c r="AC3" s="9"/>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="C4" s="9">
         <v>45764</v>
@@ -2867,12 +2848,12 @@
       <c r="AB4" s="9"/>
       <c r="AC4" s="9"/>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="C5" s="9">
         <v>45764</v>
@@ -2918,12 +2899,12 @@
       <c r="AB5" s="9"/>
       <c r="AC5" s="9"/>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="C6" s="9">
         <v>45764</v>
@@ -2967,12 +2948,12 @@
       <c r="AB6" s="9"/>
       <c r="AC6" s="9"/>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="C7" s="9">
         <v>45764</v>
@@ -3016,12 +2997,12 @@
       <c r="AB7" s="9"/>
       <c r="AC7" s="9"/>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="C8" s="9">
         <v>45764</v>
@@ -3065,12 +3046,12 @@
       <c r="AB8" s="9"/>
       <c r="AC8" s="9"/>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="C9" s="9">
         <v>46091</v>
@@ -3083,9 +3064,7 @@
       <c r="G9" s="9">
         <v>46091</v>
       </c>
-      <c r="H9" s="9">
-        <v>46091</v>
-      </c>
+      <c r="H9" s="9"/>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
@@ -3116,12 +3095,12 @@
       <c r="AB9" s="9"/>
       <c r="AC9" s="9"/>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="C10" s="9">
         <v>46091</v>
@@ -3134,9 +3113,7 @@
       <c r="G10" s="9">
         <v>46091</v>
       </c>
-      <c r="H10" s="9">
-        <v>46091</v>
-      </c>
+      <c r="H10" s="9"/>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
@@ -3167,12 +3144,12 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="C11" s="9">
         <v>46091</v>
@@ -3184,9 +3161,7 @@
       <c r="G11" s="9">
         <v>46091</v>
       </c>
-      <c r="H11" s="9">
-        <v>46091</v>
-      </c>
+      <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
@@ -3217,12 +3192,12 @@
       <c r="AB11" s="9"/>
       <c r="AC11" s="9"/>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="C12" s="9">
         <v>46091</v>
@@ -3235,9 +3210,7 @@
       <c r="G12" s="9">
         <v>46091</v>
       </c>
-      <c r="H12" s="9">
-        <v>46091</v>
-      </c>
+      <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
@@ -3268,12 +3241,12 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="C13" s="9">
         <v>46091</v>
@@ -3286,9 +3259,7 @@
       <c r="G13" s="9">
         <v>46091</v>
       </c>
-      <c r="H13" s="9">
-        <v>46091</v>
-      </c>
+      <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
@@ -3319,12 +3290,12 @@
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="C14" s="9">
         <v>46091</v>
@@ -3386,12 +3357,12 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="C15" s="9">
         <v>46091</v>
@@ -3453,12 +3424,12 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="C16" s="9">
         <v>46091</v>
@@ -3522,10 +3493,10 @@
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -3563,10 +3534,10 @@
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -8712,216 +8683,31 @@
       <c r="AB194" s="9"/>
       <c r="AC194" s="9"/>
     </row>
-    <row r="195" spans="3:29" x14ac:dyDescent="0.25">
-      <c r="C195" s="9"/>
-      <c r="D195" s="9"/>
-      <c r="E195" s="9"/>
-      <c r="F195" s="9"/>
-      <c r="G195" s="9"/>
-      <c r="H195" s="9"/>
-      <c r="I195" s="9"/>
-      <c r="J195" s="9"/>
-      <c r="K195" s="9"/>
-      <c r="L195" s="9"/>
-      <c r="M195" s="9"/>
-      <c r="N195" s="9"/>
-      <c r="O195" s="9"/>
-      <c r="P195" s="9"/>
-      <c r="Q195" s="9"/>
-      <c r="R195" s="9"/>
-      <c r="S195" s="9"/>
-      <c r="T195" s="9"/>
-      <c r="U195" s="9"/>
-      <c r="V195" s="9"/>
-      <c r="W195" s="9"/>
-      <c r="X195" s="9"/>
-      <c r="Y195" s="9"/>
-      <c r="Z195" s="9"/>
-      <c r="AA195" s="9"/>
-      <c r="AB195" s="9"/>
-      <c r="AC195" s="9"/>
-    </row>
-    <row r="196" spans="3:29" x14ac:dyDescent="0.25">
-      <c r="C196" s="9"/>
-      <c r="D196" s="9"/>
-      <c r="E196" s="9"/>
-      <c r="F196" s="9"/>
-      <c r="G196" s="9"/>
-      <c r="H196" s="9"/>
-      <c r="I196" s="9"/>
-      <c r="J196" s="9"/>
-      <c r="K196" s="9"/>
-      <c r="L196" s="9"/>
-      <c r="M196" s="9"/>
-      <c r="N196" s="9"/>
-      <c r="O196" s="9"/>
-      <c r="P196" s="9"/>
-      <c r="Q196" s="9"/>
-      <c r="R196" s="9"/>
-      <c r="S196" s="9"/>
-      <c r="T196" s="9"/>
-      <c r="U196" s="9"/>
-      <c r="V196" s="9"/>
-      <c r="W196" s="9"/>
-      <c r="X196" s="9"/>
-      <c r="Y196" s="9"/>
-      <c r="Z196" s="9"/>
-      <c r="AA196" s="9"/>
-      <c r="AB196" s="9"/>
-      <c r="AC196" s="9"/>
-    </row>
-    <row r="197" spans="3:29" x14ac:dyDescent="0.25">
-      <c r="C197" s="9"/>
-      <c r="D197" s="9"/>
-      <c r="E197" s="9"/>
-      <c r="F197" s="9"/>
-      <c r="G197" s="9"/>
-      <c r="H197" s="9"/>
-      <c r="I197" s="9"/>
-      <c r="J197" s="9"/>
-      <c r="K197" s="9"/>
-      <c r="L197" s="9"/>
-      <c r="M197" s="9"/>
-      <c r="N197" s="9"/>
-      <c r="O197" s="9"/>
-      <c r="P197" s="9"/>
-      <c r="Q197" s="9"/>
-      <c r="R197" s="9"/>
-      <c r="S197" s="9"/>
-      <c r="T197" s="9"/>
-      <c r="U197" s="9"/>
-      <c r="V197" s="9"/>
-      <c r="W197" s="9"/>
-      <c r="X197" s="9"/>
-      <c r="Y197" s="9"/>
-      <c r="Z197" s="9"/>
-      <c r="AA197" s="9"/>
-      <c r="AB197" s="9"/>
-      <c r="AC197" s="9"/>
-    </row>
-    <row r="198" spans="3:29" x14ac:dyDescent="0.25">
-      <c r="C198" s="9"/>
-      <c r="D198" s="9"/>
-      <c r="E198" s="9"/>
-      <c r="F198" s="9"/>
-      <c r="G198" s="9"/>
-      <c r="H198" s="9"/>
-      <c r="I198" s="9"/>
-      <c r="J198" s="9"/>
-      <c r="K198" s="9"/>
-      <c r="L198" s="9"/>
-      <c r="M198" s="9"/>
-      <c r="N198" s="9"/>
-      <c r="O198" s="9"/>
-      <c r="P198" s="9"/>
-      <c r="Q198" s="9"/>
-      <c r="R198" s="9"/>
-      <c r="S198" s="9"/>
-      <c r="T198" s="9"/>
-      <c r="U198" s="9"/>
-      <c r="V198" s="9"/>
-      <c r="W198" s="9"/>
-      <c r="X198" s="9"/>
-      <c r="Y198" s="9"/>
-      <c r="Z198" s="9"/>
-      <c r="AA198" s="9"/>
-      <c r="AB198" s="9"/>
-      <c r="AC198" s="9"/>
-    </row>
-    <row r="199" spans="3:29" x14ac:dyDescent="0.25">
-      <c r="C199" s="9"/>
-      <c r="D199" s="9"/>
-      <c r="E199" s="9"/>
-      <c r="F199" s="9"/>
-      <c r="G199" s="9"/>
-      <c r="H199" s="9"/>
-      <c r="I199" s="9"/>
-      <c r="J199" s="9"/>
-      <c r="K199" s="9"/>
-      <c r="L199" s="9"/>
-      <c r="M199" s="9"/>
-      <c r="N199" s="9"/>
-      <c r="O199" s="9"/>
-      <c r="P199" s="9"/>
-      <c r="Q199" s="9"/>
-      <c r="R199" s="9"/>
-      <c r="S199" s="9"/>
-      <c r="T199" s="9"/>
-      <c r="U199" s="9"/>
-      <c r="V199" s="9"/>
-      <c r="W199" s="9"/>
-      <c r="X199" s="9"/>
-      <c r="Y199" s="9"/>
-      <c r="Z199" s="9"/>
-      <c r="AA199" s="9"/>
-      <c r="AB199" s="9"/>
-      <c r="AC199" s="9"/>
-    </row>
-    <row r="200" spans="3:29" x14ac:dyDescent="0.25">
-      <c r="C200" s="9"/>
-      <c r="D200" s="9"/>
-      <c r="E200" s="9"/>
-      <c r="F200" s="9"/>
-      <c r="G200" s="9"/>
-      <c r="H200" s="9"/>
-      <c r="I200" s="9"/>
-      <c r="J200" s="9"/>
-      <c r="K200" s="9"/>
-      <c r="L200" s="9"/>
-      <c r="M200" s="9"/>
-      <c r="N200" s="9"/>
-      <c r="O200" s="9"/>
-      <c r="P200" s="9"/>
-      <c r="Q200" s="9"/>
-      <c r="R200" s="9"/>
-      <c r="S200" s="9"/>
-      <c r="T200" s="9"/>
-      <c r="U200" s="9"/>
-      <c r="V200" s="9"/>
-      <c r="W200" s="9"/>
-      <c r="X200" s="9"/>
-      <c r="Y200" s="9"/>
-      <c r="Z200" s="9"/>
-      <c r="AA200" s="9"/>
-      <c r="AB200" s="9"/>
-      <c r="AC200" s="9"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:AC200" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A2:AD200" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <mergeCells count="2">
     <mergeCell ref="C1:O1"/>
-    <mergeCell ref="P1:AC1"/>
+    <mergeCell ref="P1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="C3:AZ200">
-    <cfRule type="expression" dxfId="3" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="4" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&gt;30,(EDATE(C3,12)-TODAY())&lt;=60)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="6" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&gt;60)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
@@ -8934,93 +8720,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="A1" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="15"/>
+      <c r="A3" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="18"/>
+      <c r="E3" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F3" s="18"/>
+      <c r="G3" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" s="18"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="A4" s="20">
         <f>COUNTA(Contractors!A2:A50)</f>
         <v>2</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="14">
+      <c r="B4" s="18"/>
+      <c r="C4" s="20">
         <f>COUNTA(Workers!A2:A200)</f>
         <v>16</v>
       </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="14">
+      <c r="D4" s="18"/>
+      <c r="E4" s="20">
         <f>COUNTIFS(Workers!A2:A200,"&lt;&gt;",Workers!D2:D200,"active")</f>
         <v>16</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="14" t="str">
+      <c r="F4" s="18"/>
+      <c r="G4" s="20" t="str">
         <f ca="1">TEXT(TODAY(),"mm/dd/yyyy")</f>
-        <v>04/24/2026</v>
-      </c>
-      <c r="H4" s="15"/>
+        <v>04/27/2026</v>
+      </c>
+      <c r="H4" s="18"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
     </row>
     <row r="7" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
+      <c r="A7" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -9041,11 +8827,11 @@
         <v>2</v>
       </c>
       <c r="E9" s="3">
-        <f t="shared" ref="E9:E35" si="0">IFERROR(C9/(C9+D9),0)</f>
+        <f t="shared" ref="E9:E36" si="0">IFERROR(C9/(C9+D9),0)</f>
         <v>0.875</v>
       </c>
       <c r="F9" s="4" t="str">
-        <f t="shared" ref="F9:F35" si="1">REPT("■",ROUND(E9*20,0))</f>
+        <f t="shared" ref="F9:F36" si="1">REPT("■",ROUND(E9*20,0))</f>
         <v>■■■■■■■■■■■■■■■■■■</v>
       </c>
     </row>
@@ -9164,19 +8950,19 @@
       </c>
       <c r="C14" s="2">
         <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A14,Tracker!$C$2:$AZ$2,0))),0)</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D14" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C14</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>0.5625</v>
+        <v>0.25</v>
       </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>■■■■■■■■■■■</v>
+        <v>■■■■■</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -9721,6 +9507,32 @@
         <v>6.25E-2</v>
       </c>
       <c r="F35" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>■</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <f>Certifications!A29</f>
+        <v>0</v>
+      </c>
+      <c r="B36" s="14">
+        <f>Certifications!B29</f>
+        <v>0</v>
+      </c>
+      <c r="C36" s="14">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A36,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>1</v>
+      </c>
+      <c r="D36" s="14">
+        <f>COUNTA(Workers!A$2:A$200)-C36</f>
+        <v>15</v>
+      </c>
+      <c r="E36" s="15">
+        <f t="shared" si="0"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="F36" s="16" t="str">
         <f t="shared" si="1"/>
         <v>■</v>
       </c>
@@ -9739,14 +9551,14 @@
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E26">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>0.7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>0.7</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>

--- a/cert_tracker/Contractor Certifications Tracker.xlsx
+++ b/cert_tracker/Contractor Certifications Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsant\jacobdashboard\cert_tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7A1FC5-C730-41EA-93BF-A26A0FBA3A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D872BC-2118-46CD-B656-BE1DF9DC96CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="607" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="607" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -525,36 +525,50 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="11">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFFFE699"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFFEA4A4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -575,7 +589,21 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFEA4A4"/>
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -620,7 +648,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Contractor Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Primary Contact"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Specialty"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Workers (count)" dataDxfId="6">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Workers (count)" dataDxfId="10">
       <calculatedColumnFormula>IF(A2="","",COUNTIF(Workers!B:B,A2))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Notes"/>
@@ -8690,14 +8718,17 @@
     <mergeCell ref="P1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="C3:AZ200">
-    <cfRule type="expression" dxfId="5" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&gt;30,(EDATE(C3,12)-TODAY())&lt;=60)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&gt;60)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="1" stopIfTrue="1">
+      <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8730,42 +8761,42 @@
       <c r="F1" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="20" t="s">
         <v>89</v>
       </c>
       <c r="B3" s="18"/>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="20" t="s">
         <v>90</v>
       </c>
       <c r="D3" s="18"/>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="20" t="s">
         <v>91</v>
       </c>
       <c r="F3" s="18"/>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="20" t="s">
         <v>92</v>
       </c>
       <c r="H3" s="18"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="20">
+      <c r="A4" s="21">
         <f>COUNTA(Contractors!A2:A50)</f>
         <v>2</v>
       </c>
       <c r="B4" s="18"/>
-      <c r="C4" s="20">
+      <c r="C4" s="21">
         <f>COUNTA(Workers!A2:A200)</f>
         <v>16</v>
       </c>
       <c r="D4" s="18"/>
-      <c r="E4" s="20">
+      <c r="E4" s="21">
         <f>COUNTIFS(Workers!A2:A200,"&lt;&gt;",Workers!D2:D200,"active")</f>
         <v>16</v>
       </c>
       <c r="F4" s="18"/>
-      <c r="G4" s="20" t="str">
+      <c r="G4" s="21" t="str">
         <f ca="1">TEXT(TODAY(),"mm/dd/yyyy")</f>
-        <v>04/27/2026</v>
+        <v>04/28/2026</v>
       </c>
       <c r="H4" s="18"/>
     </row>
@@ -8780,7 +8811,7 @@
       <c r="H5" s="18"/>
     </row>
     <row r="7" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="22" t="s">
         <v>93</v>
       </c>
       <c r="B7" s="18"/>
@@ -9539,26 +9570,26 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="G4:H5"/>
+    <mergeCell ref="E4:F5"/>
+    <mergeCell ref="A7:F7"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="G4:H5"/>
-    <mergeCell ref="E4:F5"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E26">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
       <formula>0.7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="between">
       <formula>0.7</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
